--- a/business-libraries/test-data/learning_problem/assessment.xlsx
+++ b/business-libraries/test-data/learning_problem/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:Q3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,102 +419,51 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
-        <v>适用年级</v>
+        <v>施测对象*</v>
       </c>
       <c r="G1" t="str">
-        <v>适用学科</v>
+        <v>施测形式*</v>
       </c>
       <c r="H1" t="str">
-        <v>施测对象*</v>
+        <v>触发方式*</v>
       </c>
       <c r="I1" t="str">
-        <v>施测形式*</v>
+        <v>作答频次*</v>
       </c>
       <c r="J1" t="str">
-        <v>触发方式*</v>
+        <v>是否必做*</v>
       </c>
       <c r="K1" t="str">
-        <v>作答频次*</v>
+        <v>预计用时分钟*</v>
       </c>
       <c r="L1" t="str">
-        <v>是否必做*</v>
+        <v>结果可见性*</v>
       </c>
       <c r="M1" t="str">
-        <v>预计用时分钟*</v>
+        <v>数据敏感级*</v>
       </c>
       <c r="N1" t="str">
-        <v>作答时限分钟</v>
+        <v>来源属性*</v>
       </c>
       <c r="O1" t="str">
-        <v>最低题数</v>
+        <v>手册出处*</v>
       </c>
       <c r="P1" t="str">
-        <v>使用时机</v>
+        <v>版本*</v>
       </c>
       <c r="Q1" t="str">
-        <v>重评间隔天数</v>
-      </c>
-      <c r="R1" t="str">
-        <v>前置量表编码</v>
-      </c>
-      <c r="S1" t="str">
-        <v>互斥量表编码</v>
-      </c>
-      <c r="T1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="U1" t="str">
-        <v>责任角色</v>
-      </c>
-      <c r="V1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="W1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="X1" t="str">
-        <v>外部授权说明</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="AA1" t="str">
         <v>量表说明</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>常模参照</v>
-      </c>
-      <c r="AC1" t="str">
-        <v>信度说明</v>
-      </c>
-      <c r="AD1" t="str">
-        <v>效度说明</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>隐私声明</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>适用前提</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>不适合情况</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>后续建议动作</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_FIVE_Q</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B2" t="str">
-        <v>学生学习问题学习策略五问</v>
+        <v>学生学习问题三层诊断</v>
       </c>
       <c r="C2" t="str">
-        <v>学习策略</v>
+        <v>三层诊断</v>
       </c>
       <c r="D2" t="str">
         <v>learning_problem</v>
@@ -523,102 +472,51 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>teacher</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>self_report</v>
       </c>
       <c r="H2" t="str">
-        <v>teacher</v>
+        <v>manual</v>
       </c>
       <c r="I2" t="str">
-        <v>self_report</v>
+        <v>per_case</v>
       </c>
       <c r="J2" t="str">
-        <v>manual</v>
+        <v>是</v>
       </c>
       <c r="K2" t="str">
-        <v>monthly</v>
+        <v>5</v>
       </c>
       <c r="L2" t="str">
-        <v>是</v>
+        <v>teacher_only</v>
       </c>
       <c r="M2" t="str">
-        <v>3</v>
+        <v>sensitive</v>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="O2" t="str">
-        <v>5</v>
+        <v>学生学习问题手册v1</v>
       </c>
       <c r="P2" t="str">
-        <v>每月一次</v>
+        <v>1.0.0</v>
       </c>
       <c r="Q2" t="str">
-        <v>30</v>
-      </c>
-      <c r="R2" t="str">
-        <v/>
-      </c>
-      <c r="S2" t="str">
-        <v/>
-      </c>
-      <c r="T2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="U2" t="str">
-        <v>班主任本人</v>
-      </c>
-      <c r="V2" t="str">
-        <v>highly_sensitive</v>
-      </c>
-      <c r="W2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="X2" t="str">
-        <v/>
-      </c>
-      <c r="Y2" t="str">
-        <v>技术理论手册V5 第3章</v>
-      </c>
-      <c r="Z2" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="AA2" t="str">
-        <v>回顾最近一周状态，产出多维评估结果</v>
-      </c>
-      <c r="AB2" t="str">
-        <v>全国中小学班主任常模 N=3200</v>
-      </c>
-      <c r="AC2" t="str">
-        <v>Cronbach α=0.87</v>
-      </c>
-      <c r="AD2" t="str">
-        <v>与GHQ-12 相关系数 r=0.64</v>
-      </c>
-      <c r="AE2" t="str">
-        <v>数据仅用于教学支持，不用于人事考核</v>
-      </c>
-      <c r="AF2" t="str">
-        <v>适用于在职班主任，不适用于实习或代课教师</v>
-      </c>
-      <c r="AG2" t="str">
-        <v>教师正在经历重大个人变故时，建议先转介心理支持再施测</v>
-      </c>
-      <c r="AH2" t="str">
-        <v>如总分&gt;=17，建议进行深度访谈并启动个案</v>
+        <v>从行为、认知和关系三个层面识别学生学习困难的主导因素，不构成学习障碍诊断。</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_QUICK</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="B3" t="str">
-        <v>学生学习问题注意力评估</v>
+        <v>学习动机与学业情绪评估</v>
       </c>
       <c r="C3" t="str">
-        <v>注意力</v>
+        <v>动机情绪</v>
       </c>
       <c r="D3" t="str">
         <v>learning_problem</v>
@@ -627,103 +525,52 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>teacher</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>self_report</v>
       </c>
       <c r="H3" t="str">
-        <v>teacher</v>
+        <v>manual</v>
       </c>
       <c r="I3" t="str">
-        <v>self_report</v>
+        <v>per_case</v>
       </c>
       <c r="J3" t="str">
-        <v>manual</v>
+        <v>否</v>
       </c>
       <c r="K3" t="str">
-        <v>per_case</v>
+        <v>6</v>
       </c>
       <c r="L3" t="str">
-        <v>是</v>
+        <v>teacher_only</v>
       </c>
       <c r="M3" t="str">
-        <v>5</v>
+        <v>sensitive</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="O3" t="str">
-        <v>8</v>
+        <v>学生学习问题手册v1</v>
       </c>
       <c r="P3" t="str">
-        <v>学期初/学期末</v>
+        <v>1.0.0</v>
       </c>
       <c r="Q3" t="str">
-        <v>90</v>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="U3" t="str">
-        <v>班主任本人</v>
-      </c>
-      <c r="V3" t="str">
-        <v>internal</v>
-      </c>
-      <c r="W3" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="X3" t="str">
-        <v/>
-      </c>
-      <c r="Y3" t="str">
-        <v>技术理论手册V5 第4章</v>
-      </c>
-      <c r="Z3" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="AA3" t="str">
-        <v>评估教师在学生学习问题相关维度的资源与压力状况</v>
-      </c>
-      <c r="AB3" t="str">
-        <v>全国中小学班主任常模 N=2800</v>
-      </c>
-      <c r="AC3" t="str">
-        <v>Cronbach α=0.82</v>
-      </c>
-      <c r="AD3" t="str">
-        <v>内容效度经专家评审</v>
-      </c>
-      <c r="AE3" t="str">
-        <v>数据仅用于教学支持</v>
-      </c>
-      <c r="AF3" t="str">
-        <v>适用于在职班主任</v>
-      </c>
-      <c r="AG3" t="str">
-        <v>教师在严重心理危机时，建议先进行心理评估</v>
-      </c>
-      <c r="AH3" t="str">
-        <v>根据评估结果推荐相应的支持工具</v>
+        <v>在三层诊断提示关系层或行为层为主导后使用，用于区分动机类型和学业情绪状态。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AH3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:J17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -739,552 +586,546 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
-        <v>子维度</v>
+        <v>题干*</v>
       </c>
       <c r="F1" t="str">
-        <v>题干*</v>
+        <v>选项组编码*</v>
       </c>
       <c r="G1" t="str">
-        <v>题干举例</v>
+        <v>反向计分*</v>
       </c>
       <c r="H1" t="str">
-        <v>选项组编码*</v>
+        <v>权重</v>
       </c>
       <c r="I1" t="str">
-        <v>反向计分*</v>
+        <v>是否必答*</v>
       </c>
       <c r="J1" t="str">
-        <v>权重</v>
-      </c>
-      <c r="K1" t="str">
-        <v>是否必答*</v>
-      </c>
-      <c r="L1" t="str">
-        <v>显示条件</v>
-      </c>
-      <c r="M1" t="str">
         <v>数据用途*</v>
-      </c>
-      <c r="N1" t="str">
-        <v>答题提示</v>
-      </c>
-      <c r="O1" t="str">
-        <v>题目说明</v>
-      </c>
-      <c r="P1" t="str">
-        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_FIVE_Q</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B2" t="str">
-        <v>q1</v>
+        <v>beh1</v>
       </c>
       <c r="C2" t="str">
         <v>single</v>
       </c>
       <c r="D2" t="str">
-        <v>ATTENTION</v>
+        <v>行为层</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>学生经常不交或拖延完成作业。</v>
       </c>
       <c r="F2" t="str">
-        <v>这一周，我有多少时间感到学生课堂注意力和专注度？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H2" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>1</v>
-      </c>
-      <c r="K2" t="str">
-        <v>是</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
         <v>compute</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_FIVE_Q</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B3" t="str">
-        <v>q2</v>
+        <v>beh2</v>
       </c>
       <c r="C3" t="str">
         <v>single</v>
       </c>
       <c r="D3" t="str">
-        <v>STRATEGY</v>
+        <v>行为层</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>课堂上明显走神、分心或做与学习无关的事。</v>
       </c>
       <c r="F3" t="str">
-        <v>这一周，我有多少时间感到学生学习策略的使用情况？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H3" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J3" t="str">
-        <v>1</v>
-      </c>
-      <c r="K3" t="str">
-        <v>是</v>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
         <v>compute</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_FIVE_Q</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B4" t="str">
-        <v>q3</v>
+        <v>beh3</v>
       </c>
       <c r="C4" t="str">
         <v>single</v>
       </c>
       <c r="D4" t="str">
-        <v>HOMEWORK</v>
+        <v>行为层</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>考试或测验成绩与实际能力之间存在明显落差。</v>
       </c>
       <c r="F4" t="str">
-        <v>这一周，我有多少时间感到学生作业完成质量和及时性？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H4" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I4" t="str">
         <v>是</v>
       </c>
       <c r="J4" t="str">
-        <v>1</v>
-      </c>
-      <c r="K4" t="str">
-        <v>是</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
         <v>compute</v>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_FIVE_Q</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B5" t="str">
-        <v>q4</v>
+        <v>beh4</v>
       </c>
       <c r="C5" t="str">
         <v>single</v>
       </c>
       <c r="D5" t="str">
-        <v>METACOG</v>
+        <v>行为层</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>已有提醒或奖励措施对改善学习行为效果有限。</v>
       </c>
       <c r="F5" t="str">
-        <v>这一周，我有多少时间感到学生对自身学习状态的觉察与调控？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H5" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J5" t="str">
-        <v>1</v>
-      </c>
-      <c r="K5" t="str">
-        <v>是</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
         <v>compute</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_FIVE_Q</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B6" t="str">
-        <v>q5</v>
+        <v>cog1</v>
       </c>
       <c r="C6" t="str">
         <v>single</v>
       </c>
       <c r="D6" t="str">
-        <v>ENGAGEMENT</v>
+        <v>认知层</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>学生对核心概念的理解停留在表面，难以迁移或应用。</v>
       </c>
       <c r="F6" t="str">
-        <v>这一周，我有多少时间感到学生在课堂上的主动参与程度？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H6" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J6" t="str">
-        <v>1</v>
-      </c>
-      <c r="K6" t="str">
-        <v>是</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
         <v>compute</v>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>LP_QUICK</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B7" t="str">
-        <v>q1</v>
+        <v>cog2</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
       </c>
       <c r="D7" t="str">
-        <v>ATTENTION</v>
+        <v>认知层</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>学生在记忆、推理或组织信息方面存在明显困难。</v>
       </c>
       <c r="F7" t="str">
-        <v>在学生学习问题方面，评估学生课堂注意力和专注度的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H7" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J7" t="str">
-        <v>1</v>
-      </c>
-      <c r="K7" t="str">
-        <v>是</v>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
         <v>compute</v>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>LP_QUICK</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B8" t="str">
-        <v>q2</v>
+        <v>cog3</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
       </c>
       <c r="D8" t="str">
-        <v>STRATEGY</v>
+        <v>认知层</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>学生在独立解决问题时容易卡住，缺少元认知策略。</v>
       </c>
       <c r="F8" t="str">
-        <v>在学生学习问题方面，评估学生学习策略的使用情况的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H8" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J8" t="str">
-        <v>1</v>
-      </c>
-      <c r="K8" t="str">
-        <v>是</v>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
         <v>compute</v>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>LP_QUICK</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B9" t="str">
-        <v>q3</v>
+        <v>rel1</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
       </c>
       <c r="D9" t="str">
-        <v>HOMEWORK</v>
+        <v>关系层</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>师生关系或课堂归属感对学生的学习动机有明显影响。</v>
       </c>
       <c r="F9" t="str">
-        <v>在学生学习问题方面，评估学生作业完成质量和及时性的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H9" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="str">
         <v>是</v>
       </c>
       <c r="J9" t="str">
-        <v>1</v>
-      </c>
-      <c r="K9" t="str">
-        <v>是</v>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
         <v>compute</v>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>LP_QUICK</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B10" t="str">
-        <v>q4</v>
+        <v>rel2</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
       </c>
       <c r="D10" t="str">
-        <v>METACOG</v>
+        <v>关系层</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>同伴之间的比较、竞争或排斥影响了学生的学习投入。</v>
       </c>
       <c r="F10" t="str">
-        <v>在学生学习问题方面，评估学生对自身学习状态的觉察与调控的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H10" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J10" t="str">
-        <v>1</v>
-      </c>
-      <c r="K10" t="str">
-        <v>是</v>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
         <v>compute</v>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>LP_QUICK</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B11" t="str">
-        <v>q5</v>
+        <v>rel3</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
       </c>
       <c r="D11" t="str">
-        <v>ENGAGEMENT</v>
+        <v>关系层</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>家庭对学习的支持、期待或冲突明显影响了学生的学业状态。</v>
       </c>
       <c r="F11" t="str">
-        <v>在学生学习问题方面，评估学生在课堂上的主动参与程度的情况如何？</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H11" t="str">
-        <v>FREQ_5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J11" t="str">
-        <v>1</v>
-      </c>
-      <c r="K11" t="str">
-        <v>是</v>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
         <v>compute</v>
       </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v>5</v>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>LP_MOTIVATION</v>
+      </c>
+      <c r="B12" t="str">
+        <v>m1</v>
+      </c>
+      <c r="C12" t="str">
+        <v>single</v>
+      </c>
+      <c r="D12" t="str">
+        <v>内在动机</v>
+      </c>
+      <c r="E12" t="str">
+        <v>没有老师或家长督促时，学生几乎不主动学习。</v>
+      </c>
+      <c r="F12" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G12" t="str">
+        <v>否</v>
+      </c>
+      <c r="H12" t="str">
+        <v>1</v>
+      </c>
+      <c r="I12" t="str">
+        <v>是</v>
+      </c>
+      <c r="J12" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>LP_MOTIVATION</v>
+      </c>
+      <c r="B13" t="str">
+        <v>m2</v>
+      </c>
+      <c r="C13" t="str">
+        <v>single</v>
+      </c>
+      <c r="D13" t="str">
+        <v>内在动机</v>
+      </c>
+      <c r="E13" t="str">
+        <v>学生学习主要是为了避免被批评。</v>
+      </c>
+      <c r="F13" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G13" t="str">
+        <v>否</v>
+      </c>
+      <c r="H13" t="str">
+        <v>1</v>
+      </c>
+      <c r="I13" t="str">
+        <v>是</v>
+      </c>
+      <c r="J13" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LP_MOTIVATION</v>
+      </c>
+      <c r="B14" t="str">
+        <v>m3</v>
+      </c>
+      <c r="C14" t="str">
+        <v>single</v>
+      </c>
+      <c r="D14" t="str">
+        <v>学业焦虑</v>
+      </c>
+      <c r="E14" t="str">
+        <v>临近考试时学生出现明显紧张或躯体不适。</v>
+      </c>
+      <c r="F14" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G14" t="str">
+        <v>否</v>
+      </c>
+      <c r="H14" t="str">
+        <v>1</v>
+      </c>
+      <c r="I14" t="str">
+        <v>是</v>
+      </c>
+      <c r="J14" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>LP_MOTIVATION</v>
+      </c>
+      <c r="B15" t="str">
+        <v>m4</v>
+      </c>
+      <c r="C15" t="str">
+        <v>single</v>
+      </c>
+      <c r="D15" t="str">
+        <v>学业焦虑</v>
+      </c>
+      <c r="E15" t="str">
+        <v>学生因为怕出错而不敢在课堂上表达。</v>
+      </c>
+      <c r="F15" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G15" t="str">
+        <v>否</v>
+      </c>
+      <c r="H15" t="str">
+        <v>1</v>
+      </c>
+      <c r="I15" t="str">
+        <v>是</v>
+      </c>
+      <c r="J15" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>LP_MOTIVATION</v>
+      </c>
+      <c r="B16" t="str">
+        <v>m5</v>
+      </c>
+      <c r="C16" t="str">
+        <v>single</v>
+      </c>
+      <c r="D16" t="str">
+        <v>学业自我效能</v>
+      </c>
+      <c r="E16" t="str">
+        <v>学生认为自己再怎么努力也学不好某些科目。</v>
+      </c>
+      <c r="F16" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G16" t="str">
+        <v>否</v>
+      </c>
+      <c r="H16" t="str">
+        <v>1</v>
+      </c>
+      <c r="I16" t="str">
+        <v>是</v>
+      </c>
+      <c r="J16" t="str">
+        <v>compute</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>LP_MOTIVATION</v>
+      </c>
+      <c r="B17" t="str">
+        <v>m6</v>
+      </c>
+      <c r="C17" t="str">
+        <v>single</v>
+      </c>
+      <c r="D17" t="str">
+        <v>学业自我效能</v>
+      </c>
+      <c r="E17" t="str">
+        <v>学生把失败归因于自己能力不行而不是方法问题。</v>
+      </c>
+      <c r="F17" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="G17" t="str">
+        <v>否</v>
+      </c>
+      <c r="H17" t="str">
+        <v>1</v>
+      </c>
+      <c r="I17" t="str">
+        <v>是</v>
+      </c>
+      <c r="J17" t="str">
+        <v>compute</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1370,16 +1211,86 @@
         <v>5</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B7" t="str">
+        <v>1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>完全不符合</v>
+      </c>
+      <c r="D7" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2</v>
+      </c>
+      <c r="C8" t="str">
+        <v>比较不符合</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B9" t="str">
+        <v>3</v>
+      </c>
+      <c r="C9" t="str">
+        <v>一般</v>
+      </c>
+      <c r="D9" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>4</v>
+      </c>
+      <c r="C10" t="str">
+        <v>比较符合</v>
+      </c>
+      <c r="D10" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B11" t="str">
+        <v>5</v>
+      </c>
+      <c r="C11" t="str">
+        <v>非常符合</v>
+      </c>
+      <c r="D11" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:I7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1409,25 +1320,19 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
-      <c r="J1" t="str">
-        <v>常模均值</v>
-      </c>
-      <c r="K1" t="str">
-        <v>常模标准差</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_FIVE_Q</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B2" t="str">
-        <v>ATTENTION</v>
+        <v>LP_BEHAVIOR</v>
       </c>
       <c r="C2" t="str">
-        <v>注意力</v>
+        <v>行为层</v>
       </c>
       <c r="D2" t="str">
-        <v>q1</v>
+        <v>beh1,beh2,beh3,beh4</v>
       </c>
       <c r="E2" t="str">
         <v>mean</v>
@@ -1436,33 +1341,27 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>评估学生课堂注意力和专注度</v>
+        <v>行为层维度</v>
       </c>
       <c r="H2" t="str">
-        <v>&gt;=4 分：注意力良好</v>
+        <v>学习行为持续失序且外部推动无效</v>
       </c>
       <c r="I2" t="str">
-        <v>&lt;=2 分：注意力涣散</v>
-      </c>
-      <c r="J2" t="str">
-        <v>2.6</v>
-      </c>
-      <c r="K2" t="str">
-        <v>0.95</v>
+        <v>学习行为稳定</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_FIVE_Q</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B3" t="str">
-        <v>STRATEGY</v>
+        <v>LP_COGNITION</v>
       </c>
       <c r="C3" t="str">
-        <v>学习策略</v>
+        <v>认知层</v>
       </c>
       <c r="D3" t="str">
-        <v>q2</v>
+        <v>cog1,cog2,cog3</v>
       </c>
       <c r="E3" t="str">
         <v>mean</v>
@@ -1471,33 +1370,27 @@
         <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>评估学生学习策略的使用情况</v>
+        <v>认知层维度</v>
       </c>
       <c r="H3" t="str">
-        <v>&gt;=4 分：策略得当</v>
+        <v>理解停留表面，缺少元认知策略</v>
       </c>
       <c r="I3" t="str">
-        <v>&lt;=2 分：策略匮乏</v>
-      </c>
-      <c r="J3" t="str">
-        <v>2.7</v>
-      </c>
-      <c r="K3" t="str">
-        <v>0.9</v>
+        <v>认知加工顺畅</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_FIVE_Q</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B4" t="str">
-        <v>HOMEWORK</v>
+        <v>LP_RELATION</v>
       </c>
       <c r="C4" t="str">
-        <v>作业完成</v>
+        <v>关系层</v>
       </c>
       <c r="D4" t="str">
-        <v>q3</v>
+        <v>rel1,rel2,rel3</v>
       </c>
       <c r="E4" t="str">
         <v>mean</v>
@@ -1506,33 +1399,27 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>评估学生作业完成质量和及时性</v>
+        <v>关系层维度</v>
       </c>
       <c r="H4" t="str">
-        <v>&gt;=4 分：完成度好</v>
+        <v>师生、同伴或家庭关系明显影响学习投入</v>
       </c>
       <c r="I4" t="str">
-        <v>&lt;=2 分：完成度差</v>
-      </c>
-      <c r="J4" t="str">
-        <v>2.9</v>
-      </c>
-      <c r="K4" t="str">
-        <v>0.95</v>
+        <v>关系支持充分</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_FIVE_Q</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="B5" t="str">
-        <v>METACOG</v>
+        <v>LP_INTRINSIC</v>
       </c>
       <c r="C5" t="str">
-        <v>元认知</v>
+        <v>内在动机</v>
       </c>
       <c r="D5" t="str">
-        <v>q4</v>
+        <v>m1,m2</v>
       </c>
       <c r="E5" t="str">
         <v>mean</v>
@@ -1541,33 +1428,27 @@
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v>评估学生对自身学习状态的觉察与调控</v>
+        <v>内在动机维度</v>
       </c>
       <c r="H5" t="str">
-        <v>&gt;=4 分：元认知强</v>
+        <v>学习完全依赖外部推动</v>
       </c>
       <c r="I5" t="str">
-        <v>&lt;=2 分：元认知弱</v>
-      </c>
-      <c r="J5" t="str">
-        <v>2.4</v>
-      </c>
-      <c r="K5" t="str">
-        <v>0.85</v>
+        <v>有内在学习兴趣</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_FIVE_Q</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="B6" t="str">
-        <v>ENGAGEMENT</v>
+        <v>LP_ANXIETY</v>
       </c>
       <c r="C6" t="str">
-        <v>课堂参与</v>
+        <v>学业焦虑</v>
       </c>
       <c r="D6" t="str">
-        <v>q5</v>
+        <v>m3,m4</v>
       </c>
       <c r="E6" t="str">
         <v>mean</v>
@@ -1576,33 +1457,27 @@
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v>评估学生在课堂上的主动参与程度</v>
+        <v>学业焦虑维度</v>
       </c>
       <c r="H6" t="str">
-        <v>&gt;=4 分：参与积极</v>
+        <v>学业焦虑明显影响表现</v>
       </c>
       <c r="I6" t="str">
-        <v>&lt;=2 分：参与度低</v>
-      </c>
-      <c r="J6" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="K6" t="str">
-        <v>0.9</v>
+        <v>焦虑水平可控</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>LP_QUICK</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="B7" t="str">
-        <v>ATTENTION</v>
+        <v>LP_SELF_EFFICACY</v>
       </c>
       <c r="C7" t="str">
-        <v>注意力</v>
+        <v>学业自我效能</v>
       </c>
       <c r="D7" t="str">
-        <v>q1</v>
+        <v>m5,m6</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -1611,164 +1486,18 @@
         <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v>评估学生课堂注意力和专注度</v>
+        <v>学业自我效能维度</v>
       </c>
       <c r="H7" t="str">
-        <v>&gt;=4 分：注意力良好</v>
+        <v>认为自己学不会，习得性无助</v>
       </c>
       <c r="I7" t="str">
-        <v>&lt;=2 分：注意力涣散</v>
-      </c>
-      <c r="J7" t="str">
-        <v>2.6</v>
-      </c>
-      <c r="K7" t="str">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>LP_QUICK</v>
-      </c>
-      <c r="B8" t="str">
-        <v>STRATEGY</v>
-      </c>
-      <c r="C8" t="str">
-        <v>学习策略</v>
-      </c>
-      <c r="D8" t="str">
-        <v>q2</v>
-      </c>
-      <c r="E8" t="str">
-        <v>mean</v>
-      </c>
-      <c r="F8" t="str">
-        <v>1</v>
-      </c>
-      <c r="G8" t="str">
-        <v>评估学生学习策略的使用情况</v>
-      </c>
-      <c r="H8" t="str">
-        <v>&gt;=4 分：策略得当</v>
-      </c>
-      <c r="I8" t="str">
-        <v>&lt;=2 分：策略匮乏</v>
-      </c>
-      <c r="J8" t="str">
-        <v>2.7</v>
-      </c>
-      <c r="K8" t="str">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>LP_QUICK</v>
-      </c>
-      <c r="B9" t="str">
-        <v>HOMEWORK</v>
-      </c>
-      <c r="C9" t="str">
-        <v>作业完成</v>
-      </c>
-      <c r="D9" t="str">
-        <v>q3</v>
-      </c>
-      <c r="E9" t="str">
-        <v>mean</v>
-      </c>
-      <c r="F9" t="str">
-        <v>1</v>
-      </c>
-      <c r="G9" t="str">
-        <v>评估学生作业完成质量和及时性</v>
-      </c>
-      <c r="H9" t="str">
-        <v>&gt;=4 分：完成度好</v>
-      </c>
-      <c r="I9" t="str">
-        <v>&lt;=2 分：完成度差</v>
-      </c>
-      <c r="J9" t="str">
-        <v>2.9</v>
-      </c>
-      <c r="K9" t="str">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>LP_QUICK</v>
-      </c>
-      <c r="B10" t="str">
-        <v>METACOG</v>
-      </c>
-      <c r="C10" t="str">
-        <v>元认知</v>
-      </c>
-      <c r="D10" t="str">
-        <v>q4</v>
-      </c>
-      <c r="E10" t="str">
-        <v>mean</v>
-      </c>
-      <c r="F10" t="str">
-        <v>1</v>
-      </c>
-      <c r="G10" t="str">
-        <v>评估学生对自身学习状态的觉察与调控</v>
-      </c>
-      <c r="H10" t="str">
-        <v>&gt;=4 分：元认知强</v>
-      </c>
-      <c r="I10" t="str">
-        <v>&lt;=2 分：元认知弱</v>
-      </c>
-      <c r="J10" t="str">
-        <v>2.4</v>
-      </c>
-      <c r="K10" t="str">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>LP_QUICK</v>
-      </c>
-      <c r="B11" t="str">
-        <v>ENGAGEMENT</v>
-      </c>
-      <c r="C11" t="str">
-        <v>课堂参与</v>
-      </c>
-      <c r="D11" t="str">
-        <v>q5</v>
-      </c>
-      <c r="E11" t="str">
-        <v>mean</v>
-      </c>
-      <c r="F11" t="str">
-        <v>1</v>
-      </c>
-      <c r="G11" t="str">
-        <v>评估学生在课堂上的主动参与程度</v>
-      </c>
-      <c r="H11" t="str">
-        <v>&gt;=4 分：参与积极</v>
-      </c>
-      <c r="I11" t="str">
-        <v>&lt;=2 分：参与度低</v>
-      </c>
-      <c r="J11" t="str">
-        <v>2.8</v>
-      </c>
-      <c r="K11" t="str">
-        <v>0.9</v>
+        <v>相信努力有用</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/learning_problem/assessment.xlsx
+++ b/business-libraries/test-data/learning_problem/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:V3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -437,21 +437,36 @@
         <v>预计用时分钟*</v>
       </c>
       <c r="L1" t="str">
+        <v>量表角色*</v>
+      </c>
+      <c r="M1" t="str">
+        <v>前置量表编码</v>
+      </c>
+      <c r="N1" t="str">
+        <v>互斥量表编码</v>
+      </c>
+      <c r="O1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="P1" t="str">
+        <v>触发条件说明</v>
+      </c>
+      <c r="Q1" t="str">
         <v>结果可见性*</v>
       </c>
-      <c r="M1" t="str">
+      <c r="R1" t="str">
         <v>数据敏感级*</v>
       </c>
-      <c r="N1" t="str">
+      <c r="S1" t="str">
         <v>来源属性*</v>
       </c>
-      <c r="O1" t="str">
+      <c r="T1" t="str">
         <v>手册出处*</v>
       </c>
-      <c r="P1" t="str">
+      <c r="U1" t="str">
         <v>版本*</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="V1" t="str">
         <v>量表说明</v>
       </c>
     </row>
@@ -490,21 +505,36 @@
         <v>5</v>
       </c>
       <c r="L2" t="str">
+        <v>入口筛查</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
         <v>teacher_only</v>
       </c>
-      <c r="M2" t="str">
+      <c r="R2" t="str">
         <v>sensitive</v>
       </c>
-      <c r="N2" t="str">
+      <c r="S2" t="str">
         <v>proprietary</v>
       </c>
-      <c r="O2" t="str">
+      <c r="T2" t="str">
         <v>学生学习问题手册v1</v>
       </c>
-      <c r="P2" t="str">
+      <c r="U2" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="V2" t="str">
         <v>从行为、认知和关系三个层面识别学生学习困难的主导因素，不构成学习障碍诊断。</v>
       </c>
     </row>
@@ -543,27 +573,42 @@
         <v>6</v>
       </c>
       <c r="L3" t="str">
+        <v>深度诊断</v>
+      </c>
+      <c r="M3" t="str">
+        <v>LP_THREE_LAYER</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v>量表[LP_THREE_LAYER].维度[LP_RELATION] &gt;= 3 或 量表[LP_THREE_LAYER].均分 &gt;= 3.2</v>
+      </c>
+      <c r="P3" t="str">
+        <v>关系层卡点明显或三层整体偏重时，再深入测学习动机</v>
+      </c>
+      <c r="Q3" t="str">
         <v>teacher_only</v>
       </c>
-      <c r="M3" t="str">
+      <c r="R3" t="str">
         <v>sensitive</v>
       </c>
-      <c r="N3" t="str">
+      <c r="S3" t="str">
         <v>proprietary</v>
       </c>
-      <c r="O3" t="str">
+      <c r="T3" t="str">
         <v>学生学习问题手册v1</v>
       </c>
-      <c r="P3" t="str">
+      <c r="U3" t="str">
         <v>1.0.0</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="V3" t="str">
         <v>在三层诊断提示关系层或行为层为主导后使用，用于区分动机类型和学业情绪状态。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/business-libraries/test-data/learning_problem/assessment.xlsx
+++ b/business-libraries/test-data/learning_problem/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:AL3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,55 +419,103 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
+        <v>适用年级</v>
+      </c>
+      <c r="G1" t="str">
+        <v>适用学科</v>
+      </c>
+      <c r="H1" t="str">
         <v>施测对象*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>施测形式*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>触发方式*</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>作答频次*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>是否必做*</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>预计用时分钟*</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
+        <v>作答时限分钟</v>
+      </c>
+      <c r="O1" t="str">
+        <v>最低题数</v>
+      </c>
+      <c r="P1" t="str">
+        <v>使用时机</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>重评间隔天数</v>
+      </c>
+      <c r="R1" t="str">
+        <v>前置量表编码</v>
+      </c>
+      <c r="S1" t="str">
+        <v>互斥量表编码</v>
+      </c>
+      <c r="T1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="U1" t="str">
+        <v>触发条件说明</v>
+      </c>
+      <c r="V1" t="str">
+        <v>结果可见性*</v>
+      </c>
+      <c r="W1" t="str">
+        <v>责任角色</v>
+      </c>
+      <c r="X1" t="str">
+        <v>数据敏感级*</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>来源属性*</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>外部授权说明</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>手册出处*</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>版本*</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>量表说明</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>常模参照</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>信度说明</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>效度说明</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>隐私声明</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>适用前提</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>不适合情况</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>后续建议动作</v>
+      </c>
+      <c r="AK1" t="str">
         <v>量表角色*</v>
       </c>
-      <c r="M1" t="str">
-        <v>前置量表编码</v>
-      </c>
-      <c r="N1" t="str">
-        <v>互斥量表编码</v>
-      </c>
-      <c r="O1" t="str">
-        <v>触发条件</v>
-      </c>
-      <c r="P1" t="str">
-        <v>触发条件说明</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="R1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="S1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="T1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="U1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="V1" t="str">
-        <v>量表说明</v>
+      <c r="AL1" t="str">
+        <v>做完导向什么*</v>
       </c>
     </row>
     <row r="2">
@@ -487,55 +535,103 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>teacher</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>self_report</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>manual</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>per_case</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>是</v>
       </c>
-      <c r="K2" t="str">
+      <c r="M2" t="str">
         <v>5</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>从行为、认知和关系三个层面识别学生学习困难的主导因素，不构成学习障碍诊断。</v>
+      </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v/>
+      </c>
+      <c r="AI2" t="str">
+        <v/>
+      </c>
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+      <c r="AK2" t="str">
         <v>入口筛查</v>
       </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R2" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T2" t="str">
-        <v>学生学习问题手册v1</v>
-      </c>
-      <c r="U2" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V2" t="str">
-        <v>从行为、认知和关系三个层面识别学生学习困难的主导因素，不构成学习障碍诊断。</v>
+      <c r="AL2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -555,67 +651,115 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>teacher</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>self_report</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>manual</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>per_case</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>否</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v>6</v>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>LP_THREE_LAYER</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v>量表[LP_THREE_LAYER].维度[LP_RELATION] &gt;= 3 或 量表[LP_THREE_LAYER].均分 &gt;= 3.2</v>
+      </c>
+      <c r="U3" t="str">
+        <v>关系层卡点明显或三层整体偏重时，再深入测学习动机</v>
+      </c>
+      <c r="V3" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>1.0.0</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>在三层诊断提示关系层或行为层为主导后使用，用于区分动机类型和学业情绪状态。</v>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
+      <c r="AI3" t="str">
+        <v/>
+      </c>
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+      <c r="AK3" t="str">
         <v>深度诊断</v>
       </c>
-      <c r="M3" t="str">
-        <v>LP_THREE_LAYER</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v>量表[LP_THREE_LAYER].维度[LP_RELATION] &gt;= 3 或 量表[LP_THREE_LAYER].均分 &gt;= 3.2</v>
-      </c>
-      <c r="P3" t="str">
-        <v>关系层卡点明显或三层整体偏重时，再深入测学习动机</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R3" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S3" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T3" t="str">
-        <v>学生学习问题手册v1</v>
-      </c>
-      <c r="U3" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V3" t="str">
-        <v>在三层诊断提示关系层或行为层为主导后使用，用于区分动机类型和学业情绪状态。</v>
+      <c r="AL3" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:P17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -631,22 +775,40 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
+        <v>子维度</v>
+      </c>
+      <c r="F1" t="str">
         <v>题干*</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>题干举例</v>
+      </c>
+      <c r="H1" t="str">
         <v>选项组编码*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>反向计分*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>权重</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>是否必答*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
+        <v>显示条件</v>
+      </c>
+      <c r="M1" t="str">
         <v>数据用途*</v>
+      </c>
+      <c r="N1" t="str">
+        <v>答题提示</v>
+      </c>
+      <c r="O1" t="str">
+        <v>题目说明</v>
+      </c>
+      <c r="P1" t="str">
+        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
@@ -663,22 +825,40 @@
         <v>行为层</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>学生经常不交或拖延完成作业。</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>否</v>
       </c>
-      <c r="H2" t="str">
-        <v>1</v>
-      </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
+        <v>1</v>
+      </c>
+      <c r="K2" t="str">
         <v>是</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>compute</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -695,22 +875,40 @@
         <v>行为层</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>课堂上明显走神、分心或做与学习无关的事。</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>否</v>
       </c>
-      <c r="H3" t="str">
-        <v>1</v>
-      </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
+        <v>1</v>
+      </c>
+      <c r="K3" t="str">
         <v>是</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>compute</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -727,22 +925,40 @@
         <v>行为层</v>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>考试或测验成绩与实际能力之间存在明显落差。</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>否</v>
       </c>
-      <c r="H4" t="str">
-        <v>1</v>
-      </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
         <v>是</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>compute</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -759,22 +975,40 @@
         <v>行为层</v>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
         <v>已有提醒或奖励措施对改善学习行为效果有限。</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G5" t="str">
+      <c r="I5" t="str">
         <v>否</v>
       </c>
-      <c r="H5" t="str">
-        <v>1</v>
-      </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
         <v>是</v>
       </c>
-      <c r="J5" t="str">
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v>compute</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -791,22 +1025,40 @@
         <v>认知层</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
         <v>学生对核心概念的理解停留在表面，难以迁移或应用。</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G6" t="str">
+      <c r="I6" t="str">
         <v>否</v>
       </c>
-      <c r="H6" t="str">
-        <v>1</v>
-      </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
+        <v>1</v>
+      </c>
+      <c r="K6" t="str">
         <v>是</v>
       </c>
-      <c r="J6" t="str">
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v>compute</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -823,22 +1075,40 @@
         <v>认知层</v>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>学生在记忆、推理或组织信息方面存在明显困难。</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G7" t="str">
+      <c r="I7" t="str">
         <v>否</v>
       </c>
-      <c r="H7" t="str">
-        <v>1</v>
-      </c>
-      <c r="I7" t="str">
+      <c r="J7" t="str">
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
         <v>是</v>
       </c>
-      <c r="J7" t="str">
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <v>compute</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -855,22 +1125,40 @@
         <v>认知层</v>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
         <v>学生在独立解决问题时容易卡住，缺少元认知策略。</v>
       </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G8" t="str">
+      <c r="I8" t="str">
         <v>否</v>
       </c>
-      <c r="H8" t="str">
-        <v>1</v>
-      </c>
-      <c r="I8" t="str">
+      <c r="J8" t="str">
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
         <v>是</v>
       </c>
-      <c r="J8" t="str">
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
         <v>compute</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -887,22 +1175,40 @@
         <v>关系层</v>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v>师生关系或课堂归属感对学生的学习动机有明显影响。</v>
       </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G9" t="str">
+      <c r="I9" t="str">
         <v>否</v>
       </c>
-      <c r="H9" t="str">
-        <v>1</v>
-      </c>
-      <c r="I9" t="str">
+      <c r="J9" t="str">
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
         <v>是</v>
       </c>
-      <c r="J9" t="str">
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <v>compute</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -919,22 +1225,40 @@
         <v>关系层</v>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
         <v>同伴之间的比较、竞争或排斥影响了学生的学习投入。</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G10" t="str">
+      <c r="I10" t="str">
         <v>否</v>
       </c>
-      <c r="H10" t="str">
-        <v>1</v>
-      </c>
-      <c r="I10" t="str">
+      <c r="J10" t="str">
+        <v>1</v>
+      </c>
+      <c r="K10" t="str">
         <v>是</v>
       </c>
-      <c r="J10" t="str">
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
         <v>compute</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -951,22 +1275,40 @@
         <v>关系层</v>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>家庭对学习的支持、期待或冲突明显影响了学生的学业状态。</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G11" t="str">
+      <c r="I11" t="str">
         <v>否</v>
       </c>
-      <c r="H11" t="str">
-        <v>1</v>
-      </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
+        <v>1</v>
+      </c>
+      <c r="K11" t="str">
         <v>是</v>
       </c>
-      <c r="J11" t="str">
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v>compute</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -983,22 +1325,40 @@
         <v>内在动机</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
         <v>没有老师或家长督促时，学生几乎不主动学习。</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G12" t="str">
+      <c r="I12" t="str">
         <v>否</v>
       </c>
-      <c r="H12" t="str">
-        <v>1</v>
-      </c>
-      <c r="I12" t="str">
+      <c r="J12" t="str">
+        <v>1</v>
+      </c>
+      <c r="K12" t="str">
         <v>是</v>
       </c>
-      <c r="J12" t="str">
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <v>compute</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -1015,22 +1375,40 @@
         <v>内在动机</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
         <v>学生学习主要是为了避免被批评。</v>
       </c>
-      <c r="F13" t="str">
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G13" t="str">
+      <c r="I13" t="str">
         <v>否</v>
       </c>
-      <c r="H13" t="str">
-        <v>1</v>
-      </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
+        <v>1</v>
+      </c>
+      <c r="K13" t="str">
         <v>是</v>
       </c>
-      <c r="J13" t="str">
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v>compute</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -1047,22 +1425,40 @@
         <v>学业焦虑</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
         <v>临近考试时学生出现明显紧张或躯体不适。</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G14" t="str">
+      <c r="I14" t="str">
         <v>否</v>
       </c>
-      <c r="H14" t="str">
-        <v>1</v>
-      </c>
-      <c r="I14" t="str">
+      <c r="J14" t="str">
+        <v>1</v>
+      </c>
+      <c r="K14" t="str">
         <v>是</v>
       </c>
-      <c r="J14" t="str">
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <v>compute</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -1079,22 +1475,40 @@
         <v>学业焦虑</v>
       </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
         <v>学生因为怕出错而不敢在课堂上表达。</v>
       </c>
-      <c r="F15" t="str">
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G15" t="str">
+      <c r="I15" t="str">
         <v>否</v>
       </c>
-      <c r="H15" t="str">
-        <v>1</v>
-      </c>
-      <c r="I15" t="str">
+      <c r="J15" t="str">
+        <v>1</v>
+      </c>
+      <c r="K15" t="str">
         <v>是</v>
       </c>
-      <c r="J15" t="str">
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
         <v>compute</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -1111,22 +1525,40 @@
         <v>学业自我效能</v>
       </c>
       <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
         <v>学生认为自己再怎么努力也学不好某些科目。</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G16" t="str">
+      <c r="I16" t="str">
         <v>否</v>
       </c>
-      <c r="H16" t="str">
-        <v>1</v>
-      </c>
-      <c r="I16" t="str">
+      <c r="J16" t="str">
+        <v>1</v>
+      </c>
+      <c r="K16" t="str">
         <v>是</v>
       </c>
-      <c r="J16" t="str">
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
         <v>compute</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -1143,27 +1575,45 @@
         <v>学业自我效能</v>
       </c>
       <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
         <v>学生把失败归因于自己能力不行而不是方法问题。</v>
       </c>
-      <c r="F17" t="str">
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="G17" t="str">
+      <c r="I17" t="str">
         <v>否</v>
       </c>
-      <c r="H17" t="str">
-        <v>1</v>
-      </c>
-      <c r="I17" t="str">
+      <c r="J17" t="str">
+        <v>1</v>
+      </c>
+      <c r="K17" t="str">
         <v>是</v>
       </c>
-      <c r="J17" t="str">
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
         <v>compute</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P17"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1335,7 +1785,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:K7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1365,6 +1815,12 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
+      <c r="J1" t="str">
+        <v>常模均值</v>
+      </c>
+      <c r="K1" t="str">
+        <v>常模标准差</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1394,6 +1850,12 @@
       <c r="I2" t="str">
         <v>学习行为稳定</v>
       </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -1423,6 +1885,12 @@
       <c r="I3" t="str">
         <v>认知加工顺畅</v>
       </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -1452,6 +1920,12 @@
       <c r="I4" t="str">
         <v>关系支持充分</v>
       </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -1481,6 +1955,12 @@
       <c r="I5" t="str">
         <v>有内在学习兴趣</v>
       </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -1510,6 +1990,12 @@
       <c r="I6" t="str">
         <v>焦虑水平可控</v>
       </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -1539,10 +2025,16 @@
       <c r="I7" t="str">
         <v>相信努力有用</v>
       </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/learning_problem/assessment.xlsx
+++ b/business-libraries/test-data/learning_problem/assessment.xlsx
@@ -520,7 +520,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B2" t="str">
         <v>学生学习问题三层诊断</v>
@@ -586,7 +586,7 @@
         <v>teacher_only</v>
       </c>
       <c r="W2" t="str">
-        <v/>
+        <v>班主任</v>
       </c>
       <c r="X2" t="str">
         <v>sensitive</v>
@@ -601,7 +601,7 @@
         <v>学生学习问题手册v1</v>
       </c>
       <c r="AB2" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AC2" t="str">
         <v>从行为、认知和关系三个层面识别学生学习困难的主导因素，不构成学习障碍诊断。</v>
@@ -631,12 +631,12 @@
         <v>入口筛查</v>
       </c>
       <c r="AL2" t="str">
-        <v/>
+        <v>决定要不要往下做深度诊断</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B3" t="str">
         <v>学习动机与学业情绪评估</v>
@@ -687,13 +687,13 @@
         <v/>
       </c>
       <c r="R3" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="S3" t="str">
         <v/>
       </c>
       <c r="T3" t="str">
-        <v>量表[LP_THREE_LAYER].维度[LP_RELATION] &gt;= 3 或 量表[LP_THREE_LAYER].均分 &gt;= 3.2</v>
+        <v>量表[LP_S1].维度[LP_S1D3] &gt;= 3 或 量表[LP_S1].均分 &gt;= 3.2</v>
       </c>
       <c r="U3" t="str">
         <v>关系层卡点明显或三层整体偏重时，再深入测学习动机</v>
@@ -702,7 +702,7 @@
         <v>teacher_only</v>
       </c>
       <c r="W3" t="str">
-        <v/>
+        <v>班主任</v>
       </c>
       <c r="X3" t="str">
         <v>sensitive</v>
@@ -717,10 +717,10 @@
         <v>学生学习问题手册v1</v>
       </c>
       <c r="AB3" t="str">
-        <v>1.0.0</v>
+        <v>4.0.0</v>
       </c>
       <c r="AC3" t="str">
-        <v>在三层诊断提示关系层或行为层为主导后使用，用于区分动机类型和学业情绪状态。</v>
+        <v>关系层卡点明显或三层整体偏重时，再深入测学习动机</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -747,7 +747,7 @@
         <v>深度诊断</v>
       </c>
       <c r="AL3" t="str">
-        <v/>
+        <v>定位薄弱维度，匹配对应工具</v>
       </c>
     </row>
   </sheetData>
@@ -813,10 +813,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>beh1</v>
+        <v>q1</v>
       </c>
       <c r="C2" t="str">
         <v>single</v>
@@ -863,10 +863,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>beh2</v>
+        <v>q2</v>
       </c>
       <c r="C3" t="str">
         <v>single</v>
@@ -913,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>beh3</v>
+        <v>q3</v>
       </c>
       <c r="C4" t="str">
         <v>single</v>
@@ -963,10 +963,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B5" t="str">
-        <v>beh4</v>
+        <v>q4</v>
       </c>
       <c r="C5" t="str">
         <v>single</v>
@@ -1013,10 +1013,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B6" t="str">
-        <v>cog1</v>
+        <v>q5</v>
       </c>
       <c r="C6" t="str">
         <v>single</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B7" t="str">
-        <v>cog2</v>
+        <v>q6</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B8" t="str">
-        <v>cog3</v>
+        <v>q7</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
@@ -1163,10 +1163,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B9" t="str">
-        <v>rel1</v>
+        <v>q8</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
@@ -1213,10 +1213,10 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B10" t="str">
-        <v>rel2</v>
+        <v>q9</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
@@ -1263,10 +1263,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B11" t="str">
-        <v>rel3</v>
+        <v>q10</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B12" t="str">
-        <v>m1</v>
+        <v>q1</v>
       </c>
       <c r="C12" t="str">
         <v>single</v>
@@ -1363,10 +1363,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B13" t="str">
-        <v>m2</v>
+        <v>q2</v>
       </c>
       <c r="C13" t="str">
         <v>single</v>
@@ -1413,10 +1413,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B14" t="str">
-        <v>m3</v>
+        <v>q3</v>
       </c>
       <c r="C14" t="str">
         <v>single</v>
@@ -1463,10 +1463,10 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B15" t="str">
-        <v>m4</v>
+        <v>q4</v>
       </c>
       <c r="C15" t="str">
         <v>single</v>
@@ -1513,10 +1513,10 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B16" t="str">
-        <v>m5</v>
+        <v>q5</v>
       </c>
       <c r="C16" t="str">
         <v>single</v>
@@ -1563,10 +1563,10 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B17" t="str">
-        <v>m6</v>
+        <v>q6</v>
       </c>
       <c r="C17" t="str">
         <v>single</v>
@@ -1620,7 +1620,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1638,13 +1638,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>几乎没有</v>
+        <v>完全不符合</v>
       </c>
       <c r="D2" t="str">
         <v>1</v>
@@ -1652,13 +1652,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>很少</v>
+        <v>比较不符合</v>
       </c>
       <c r="D3" t="str">
         <v>2</v>
@@ -1666,13 +1666,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>有时</v>
+        <v>一般</v>
       </c>
       <c r="D4" t="str">
         <v>3</v>
@@ -1680,13 +1680,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>经常</v>
+        <v>比较符合</v>
       </c>
       <c r="D5" t="str">
         <v>4</v>
@@ -1694,91 +1694,21 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B6" t="str">
         <v>5</v>
       </c>
       <c r="C6" t="str">
-        <v>几乎每天</v>
+        <v>非常符合</v>
       </c>
       <c r="D6" t="str">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B7" t="str">
-        <v>1</v>
-      </c>
-      <c r="C7" t="str">
-        <v>完全不符合</v>
-      </c>
-      <c r="D7" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2</v>
-      </c>
-      <c r="C8" t="str">
-        <v>比较不符合</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B9" t="str">
-        <v>3</v>
-      </c>
-      <c r="C9" t="str">
-        <v>一般</v>
-      </c>
-      <c r="D9" t="str">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B10" t="str">
-        <v>4</v>
-      </c>
-      <c r="C10" t="str">
-        <v>比较符合</v>
-      </c>
-      <c r="D10" t="str">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B11" t="str">
-        <v>5</v>
-      </c>
-      <c r="C11" t="str">
-        <v>非常符合</v>
-      </c>
-      <c r="D11" t="str">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1824,16 +1754,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>LP_BEHAVIOR</v>
+        <v>LP_S1D1</v>
       </c>
       <c r="C2" t="str">
         <v>行为层</v>
       </c>
       <c r="D2" t="str">
-        <v>beh1,beh2,beh3,beh4</v>
+        <v>q1,q2,q3,q4</v>
       </c>
       <c r="E2" t="str">
         <v>mean</v>
@@ -1859,16 +1789,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>LP_COGNITION</v>
+        <v>LP_S1D2</v>
       </c>
       <c r="C3" t="str">
         <v>认知层</v>
       </c>
       <c r="D3" t="str">
-        <v>cog1,cog2,cog3</v>
+        <v>q5,q6,q7</v>
       </c>
       <c r="E3" t="str">
         <v>mean</v>
@@ -1894,16 +1824,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>LP_RELATION</v>
+        <v>LP_S1D3</v>
       </c>
       <c r="C4" t="str">
         <v>关系层</v>
       </c>
       <c r="D4" t="str">
-        <v>rel1,rel2,rel3</v>
+        <v>q8,q9,q10</v>
       </c>
       <c r="E4" t="str">
         <v>mean</v>
@@ -1929,16 +1859,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B5" t="str">
-        <v>LP_INTRINSIC</v>
+        <v>LP_S2D1</v>
       </c>
       <c r="C5" t="str">
         <v>内在动机</v>
       </c>
       <c r="D5" t="str">
-        <v>m1,m2</v>
+        <v>q1,q2</v>
       </c>
       <c r="E5" t="str">
         <v>mean</v>
@@ -1964,16 +1894,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B6" t="str">
-        <v>LP_ANXIETY</v>
+        <v>LP_S2D2</v>
       </c>
       <c r="C6" t="str">
         <v>学业焦虑</v>
       </c>
       <c r="D6" t="str">
-        <v>m3,m4</v>
+        <v>q3,q4</v>
       </c>
       <c r="E6" t="str">
         <v>mean</v>
@@ -1999,16 +1929,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B7" t="str">
-        <v>LP_SELF_EFFICACY</v>
+        <v>LP_S2D3</v>
       </c>
       <c r="C7" t="str">
         <v>学业自我效能</v>
       </c>
       <c r="D7" t="str">
-        <v>m5,m6</v>
+        <v>q5,q6</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>

--- a/business-libraries/test-data/learning_problem/assessment.xlsx
+++ b/business-libraries/test-data/learning_problem/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL3"/>
+  <dimension ref="A1:V3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,108 +419,60 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
-        <v>适用年级</v>
+        <v>施测对象*</v>
       </c>
       <c r="G1" t="str">
-        <v>适用学科</v>
+        <v>施测形式*</v>
       </c>
       <c r="H1" t="str">
-        <v>施测对象*</v>
+        <v>触发方式*</v>
       </c>
       <c r="I1" t="str">
-        <v>施测形式*</v>
+        <v>作答频次*</v>
       </c>
       <c r="J1" t="str">
-        <v>触发方式*</v>
+        <v>是否必做*</v>
       </c>
       <c r="K1" t="str">
-        <v>作答频次*</v>
+        <v>预计用时分钟*</v>
       </c>
       <c r="L1" t="str">
-        <v>是否必做*</v>
+        <v>量表角色*</v>
       </c>
       <c r="M1" t="str">
-        <v>预计用时分钟*</v>
+        <v>前置量表编码</v>
       </c>
       <c r="N1" t="str">
-        <v>作答时限分钟</v>
+        <v>互斥量表编码</v>
       </c>
       <c r="O1" t="str">
-        <v>最低题数</v>
+        <v>触发条件</v>
       </c>
       <c r="P1" t="str">
-        <v>使用时机</v>
+        <v>触发条件说明</v>
       </c>
       <c r="Q1" t="str">
-        <v>重评间隔天数</v>
+        <v>结果可见性*</v>
       </c>
       <c r="R1" t="str">
-        <v>前置量表编码</v>
+        <v>数据敏感级*</v>
       </c>
       <c r="S1" t="str">
-        <v>互斥量表编码</v>
+        <v>来源属性*</v>
       </c>
       <c r="T1" t="str">
-        <v>触发条件</v>
+        <v>手册出处*</v>
       </c>
       <c r="U1" t="str">
-        <v>触发条件说明</v>
+        <v>版本*</v>
       </c>
       <c r="V1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="W1" t="str">
-        <v>责任角色</v>
-      </c>
-      <c r="X1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>外部授权说明</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="AC1" t="str">
         <v>量表说明</v>
-      </c>
-      <c r="AD1" t="str">
-        <v>常模参照</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>信度说明</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>效度说明</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>隐私声明</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>适用前提</v>
-      </c>
-      <c r="AI1" t="str">
-        <v>不适合情况</v>
-      </c>
-      <c r="AJ1" t="str">
-        <v>后续建议动作</v>
-      </c>
-      <c r="AK1" t="str">
-        <v>量表角色*</v>
-      </c>
-      <c r="AL1" t="str">
-        <v>做完导向什么*</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B2" t="str">
         <v>学生学习问题三层诊断</v>
@@ -535,28 +487,28 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="G2" t="str">
+        <v>self_report</v>
+      </c>
+      <c r="H2" t="str">
+        <v>manual</v>
+      </c>
+      <c r="I2" t="str">
+        <v>per_case</v>
+      </c>
+      <c r="J2" t="str">
+        <v>是</v>
+      </c>
+      <c r="K2" t="str">
+        <v>5</v>
+      </c>
+      <c r="L2" t="str">
+        <v>入口筛查</v>
+      </c>
+      <c r="M2" t="str">
         <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v>teacher</v>
-      </c>
-      <c r="I2" t="str">
-        <v>self_report</v>
-      </c>
-      <c r="J2" t="str">
-        <v>manual</v>
-      </c>
-      <c r="K2" t="str">
-        <v>per_case</v>
-      </c>
-      <c r="L2" t="str">
-        <v>是</v>
-      </c>
-      <c r="M2" t="str">
-        <v>5</v>
       </c>
       <c r="N2" t="str">
         <v/>
@@ -568,75 +520,27 @@
         <v/>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>teacher_only</v>
       </c>
       <c r="R2" t="str">
-        <v/>
+        <v>sensitive</v>
       </c>
       <c r="S2" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="T2" t="str">
-        <v/>
+        <v>学生学习问题手册v1</v>
       </c>
       <c r="U2" t="str">
-        <v/>
+        <v>1.0.0</v>
       </c>
       <c r="V2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="W2" t="str">
-        <v>班主任</v>
-      </c>
-      <c r="X2" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="Y2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="Z2" t="str">
-        <v/>
-      </c>
-      <c r="AA2" t="str">
-        <v>学生学习问题手册v1</v>
-      </c>
-      <c r="AB2" t="str">
-        <v>4.0.0</v>
-      </c>
-      <c r="AC2" t="str">
         <v>从行为、认知和关系三个层面识别学生学习困难的主导因素，不构成学习障碍诊断。</v>
-      </c>
-      <c r="AD2" t="str">
-        <v/>
-      </c>
-      <c r="AE2" t="str">
-        <v/>
-      </c>
-      <c r="AF2" t="str">
-        <v/>
-      </c>
-      <c r="AG2" t="str">
-        <v/>
-      </c>
-      <c r="AH2" t="str">
-        <v/>
-      </c>
-      <c r="AI2" t="str">
-        <v/>
-      </c>
-      <c r="AJ2" t="str">
-        <v/>
-      </c>
-      <c r="AK2" t="str">
-        <v>入口筛查</v>
-      </c>
-      <c r="AL2" t="str">
-        <v>决定要不要往下做深度诊断</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="B3" t="str">
         <v>学习动机与学业情绪评估</v>
@@ -651,115 +555,67 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>teacher</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>self_report</v>
       </c>
       <c r="H3" t="str">
-        <v>teacher</v>
+        <v>manual</v>
       </c>
       <c r="I3" t="str">
-        <v>self_report</v>
+        <v>per_case</v>
       </c>
       <c r="J3" t="str">
-        <v>manual</v>
+        <v>否</v>
       </c>
       <c r="K3" t="str">
-        <v>per_case</v>
+        <v>6</v>
       </c>
       <c r="L3" t="str">
-        <v>否</v>
+        <v>深度诊断</v>
       </c>
       <c r="M3" t="str">
-        <v>6</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="N3" t="str">
         <v/>
       </c>
       <c r="O3" t="str">
-        <v/>
+        <v>量表[LP_THREE_LAYER].维度[LP_RELATION] &gt;= 3 或 量表[LP_THREE_LAYER].均分 &gt;= 3.2</v>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>关系层卡点明显或三层整体偏重时，再深入测学习动机</v>
       </c>
       <c r="Q3" t="str">
-        <v/>
+        <v>teacher_only</v>
       </c>
       <c r="R3" t="str">
-        <v>LP_S1</v>
+        <v>sensitive</v>
       </c>
       <c r="S3" t="str">
-        <v/>
+        <v>proprietary</v>
       </c>
       <c r="T3" t="str">
-        <v>量表[LP_S1].维度[LP_S1D3] &gt;= 3 或 量表[LP_S1].均分 &gt;= 3.2</v>
+        <v>学生学习问题手册v1</v>
       </c>
       <c r="U3" t="str">
-        <v>关系层卡点明显或三层整体偏重时，再深入测学习动机</v>
+        <v>1.0.0</v>
       </c>
       <c r="V3" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="W3" t="str">
-        <v>班主任</v>
-      </c>
-      <c r="X3" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="Y3" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="Z3" t="str">
-        <v/>
-      </c>
-      <c r="AA3" t="str">
-        <v>学生学习问题手册v1</v>
-      </c>
-      <c r="AB3" t="str">
-        <v>4.0.0</v>
-      </c>
-      <c r="AC3" t="str">
-        <v>关系层卡点明显或三层整体偏重时，再深入测学习动机</v>
-      </c>
-      <c r="AD3" t="str">
-        <v/>
-      </c>
-      <c r="AE3" t="str">
-        <v/>
-      </c>
-      <c r="AF3" t="str">
-        <v/>
-      </c>
-      <c r="AG3" t="str">
-        <v/>
-      </c>
-      <c r="AH3" t="str">
-        <v/>
-      </c>
-      <c r="AI3" t="str">
-        <v/>
-      </c>
-      <c r="AJ3" t="str">
-        <v/>
-      </c>
-      <c r="AK3" t="str">
-        <v>深度诊断</v>
-      </c>
-      <c r="AL3" t="str">
-        <v>定位薄弱维度，匹配对应工具</v>
+        <v>在三层诊断提示关系层或行为层为主导后使用，用于区分动机类型和学业情绪状态。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AL3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:J17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -775,48 +631,30 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
-        <v>子维度</v>
+        <v>题干*</v>
       </c>
       <c r="F1" t="str">
-        <v>题干*</v>
+        <v>选项组编码*</v>
       </c>
       <c r="G1" t="str">
-        <v>题干举例</v>
+        <v>反向计分*</v>
       </c>
       <c r="H1" t="str">
-        <v>选项组编码*</v>
+        <v>权重</v>
       </c>
       <c r="I1" t="str">
-        <v>反向计分*</v>
+        <v>是否必答*</v>
       </c>
       <c r="J1" t="str">
-        <v>权重</v>
-      </c>
-      <c r="K1" t="str">
-        <v>是否必答*</v>
-      </c>
-      <c r="L1" t="str">
-        <v>显示条件</v>
-      </c>
-      <c r="M1" t="str">
         <v>数据用途*</v>
-      </c>
-      <c r="N1" t="str">
-        <v>答题提示</v>
-      </c>
-      <c r="O1" t="str">
-        <v>题目说明</v>
-      </c>
-      <c r="P1" t="str">
-        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B2" t="str">
-        <v>q1</v>
+        <v>beh1</v>
       </c>
       <c r="C2" t="str">
         <v>single</v>
@@ -825,48 +663,30 @@
         <v>行为层</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>学生经常不交或拖延完成作业。</v>
       </c>
       <c r="F2" t="str">
-        <v>学生经常不交或拖延完成作业。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H2" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J2" t="str">
-        <v>1</v>
-      </c>
-      <c r="K2" t="str">
-        <v>是</v>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
         <v>compute</v>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B3" t="str">
-        <v>q2</v>
+        <v>beh2</v>
       </c>
       <c r="C3" t="str">
         <v>single</v>
@@ -875,48 +695,30 @@
         <v>行为层</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>课堂上明显走神、分心或做与学习无关的事。</v>
       </c>
       <c r="F3" t="str">
-        <v>课堂上明显走神、分心或做与学习无关的事。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H3" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J3" t="str">
-        <v>1</v>
-      </c>
-      <c r="K3" t="str">
-        <v>是</v>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
         <v>compute</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B4" t="str">
-        <v>q3</v>
+        <v>beh3</v>
       </c>
       <c r="C4" t="str">
         <v>single</v>
@@ -925,48 +727,30 @@
         <v>行为层</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>考试或测验成绩与实际能力之间存在明显落差。</v>
       </c>
       <c r="F4" t="str">
-        <v>考试或测验成绩与实际能力之间存在明显落差。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H4" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I4" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J4" t="str">
-        <v>1</v>
-      </c>
-      <c r="K4" t="str">
-        <v>是</v>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
         <v>compute</v>
-      </c>
-      <c r="N4" t="str">
-        <v/>
-      </c>
-      <c r="O4" t="str">
-        <v/>
-      </c>
-      <c r="P4" t="str">
-        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B5" t="str">
-        <v>q4</v>
+        <v>beh4</v>
       </c>
       <c r="C5" t="str">
         <v>single</v>
@@ -975,48 +759,30 @@
         <v>行为层</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>已有提醒或奖励措施对改善学习行为效果有限。</v>
       </c>
       <c r="F5" t="str">
-        <v>已有提醒或奖励措施对改善学习行为效果有限。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H5" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I5" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J5" t="str">
-        <v>1</v>
-      </c>
-      <c r="K5" t="str">
-        <v>是</v>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
         <v>compute</v>
-      </c>
-      <c r="N5" t="str">
-        <v/>
-      </c>
-      <c r="O5" t="str">
-        <v/>
-      </c>
-      <c r="P5" t="str">
-        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B6" t="str">
-        <v>q5</v>
+        <v>cog1</v>
       </c>
       <c r="C6" t="str">
         <v>single</v>
@@ -1025,48 +791,30 @@
         <v>认知层</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>学生对核心概念的理解停留在表面，难以迁移或应用。</v>
       </c>
       <c r="F6" t="str">
-        <v>学生对核心概念的理解停留在表面，难以迁移或应用。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H6" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I6" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J6" t="str">
-        <v>1</v>
-      </c>
-      <c r="K6" t="str">
-        <v>是</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
         <v>compute</v>
-      </c>
-      <c r="N6" t="str">
-        <v/>
-      </c>
-      <c r="O6" t="str">
-        <v/>
-      </c>
-      <c r="P6" t="str">
-        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B7" t="str">
-        <v>q6</v>
+        <v>cog2</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
@@ -1075,48 +823,30 @@
         <v>认知层</v>
       </c>
       <c r="E7" t="str">
-        <v/>
+        <v>学生在记忆、推理或组织信息方面存在明显困难。</v>
       </c>
       <c r="F7" t="str">
-        <v>学生在记忆、推理或组织信息方面存在明显困难。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H7" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I7" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J7" t="str">
-        <v>1</v>
-      </c>
-      <c r="K7" t="str">
-        <v>是</v>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
         <v>compute</v>
-      </c>
-      <c r="N7" t="str">
-        <v/>
-      </c>
-      <c r="O7" t="str">
-        <v/>
-      </c>
-      <c r="P7" t="str">
-        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B8" t="str">
-        <v>q7</v>
+        <v>cog3</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
@@ -1125,48 +855,30 @@
         <v>认知层</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>学生在独立解决问题时容易卡住，缺少元认知策略。</v>
       </c>
       <c r="F8" t="str">
-        <v>学生在独立解决问题时容易卡住，缺少元认知策略。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H8" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I8" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J8" t="str">
-        <v>1</v>
-      </c>
-      <c r="K8" t="str">
-        <v>是</v>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
         <v>compute</v>
-      </c>
-      <c r="N8" t="str">
-        <v/>
-      </c>
-      <c r="O8" t="str">
-        <v/>
-      </c>
-      <c r="P8" t="str">
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B9" t="str">
-        <v>q8</v>
+        <v>rel1</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
@@ -1175,48 +887,30 @@
         <v>关系层</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>师生关系或课堂归属感对学生的学习动机有明显影响。</v>
       </c>
       <c r="F9" t="str">
-        <v>师生关系或课堂归属感对学生的学习动机有明显影响。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H9" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J9" t="str">
-        <v>1</v>
-      </c>
-      <c r="K9" t="str">
-        <v>是</v>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
         <v>compute</v>
-      </c>
-      <c r="N9" t="str">
-        <v/>
-      </c>
-      <c r="O9" t="str">
-        <v/>
-      </c>
-      <c r="P9" t="str">
-        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B10" t="str">
-        <v>q9</v>
+        <v>rel2</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
@@ -1225,48 +919,30 @@
         <v>关系层</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>同伴之间的比较、竞争或排斥影响了学生的学习投入。</v>
       </c>
       <c r="F10" t="str">
-        <v>同伴之间的比较、竞争或排斥影响了学生的学习投入。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H10" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I10" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J10" t="str">
-        <v>1</v>
-      </c>
-      <c r="K10" t="str">
-        <v>是</v>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
         <v>compute</v>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B11" t="str">
-        <v>q10</v>
+        <v>rel3</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
@@ -1275,48 +951,30 @@
         <v>关系层</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>家庭对学习的支持、期待或冲突明显影响了学生的学业状态。</v>
       </c>
       <c r="F11" t="str">
-        <v>家庭对学习的支持、期待或冲突明显影响了学生的学业状态。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H11" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J11" t="str">
-        <v>1</v>
-      </c>
-      <c r="K11" t="str">
-        <v>是</v>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
         <v>compute</v>
-      </c>
-      <c r="N11" t="str">
-        <v/>
-      </c>
-      <c r="O11" t="str">
-        <v/>
-      </c>
-      <c r="P11" t="str">
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="B12" t="str">
-        <v>q1</v>
+        <v>m1</v>
       </c>
       <c r="C12" t="str">
         <v>single</v>
@@ -1325,48 +983,30 @@
         <v>内在动机</v>
       </c>
       <c r="E12" t="str">
-        <v/>
+        <v>没有老师或家长督促时，学生几乎不主动学习。</v>
       </c>
       <c r="F12" t="str">
-        <v>没有老师或家长督促时，学生几乎不主动学习。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H12" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I12" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J12" t="str">
-        <v>1</v>
-      </c>
-      <c r="K12" t="str">
-        <v>是</v>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
-      <c r="M12" t="str">
         <v>compute</v>
-      </c>
-      <c r="N12" t="str">
-        <v/>
-      </c>
-      <c r="O12" t="str">
-        <v/>
-      </c>
-      <c r="P12" t="str">
-        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="B13" t="str">
-        <v>q2</v>
+        <v>m2</v>
       </c>
       <c r="C13" t="str">
         <v>single</v>
@@ -1375,48 +1015,30 @@
         <v>内在动机</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>学生学习主要是为了避免被批评。</v>
       </c>
       <c r="F13" t="str">
-        <v>学生学习主要是为了避免被批评。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H13" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I13" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J13" t="str">
-        <v>1</v>
-      </c>
-      <c r="K13" t="str">
-        <v>是</v>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13" t="str">
         <v>compute</v>
-      </c>
-      <c r="N13" t="str">
-        <v/>
-      </c>
-      <c r="O13" t="str">
-        <v/>
-      </c>
-      <c r="P13" t="str">
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="B14" t="str">
-        <v>q3</v>
+        <v>m3</v>
       </c>
       <c r="C14" t="str">
         <v>single</v>
@@ -1425,48 +1047,30 @@
         <v>学业焦虑</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>临近考试时学生出现明显紧张或躯体不适。</v>
       </c>
       <c r="F14" t="str">
-        <v>临近考试时学生出现明显紧张或躯体不适。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H14" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I14" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J14" t="str">
-        <v>1</v>
-      </c>
-      <c r="K14" t="str">
-        <v>是</v>
-      </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
-      <c r="M14" t="str">
         <v>compute</v>
-      </c>
-      <c r="N14" t="str">
-        <v/>
-      </c>
-      <c r="O14" t="str">
-        <v/>
-      </c>
-      <c r="P14" t="str">
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="B15" t="str">
-        <v>q4</v>
+        <v>m4</v>
       </c>
       <c r="C15" t="str">
         <v>single</v>
@@ -1475,48 +1079,30 @@
         <v>学业焦虑</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>学生因为怕出错而不敢在课堂上表达。</v>
       </c>
       <c r="F15" t="str">
-        <v>学生因为怕出错而不敢在课堂上表达。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H15" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I15" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J15" t="str">
-        <v>1</v>
-      </c>
-      <c r="K15" t="str">
-        <v>是</v>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
         <v>compute</v>
-      </c>
-      <c r="N15" t="str">
-        <v/>
-      </c>
-      <c r="O15" t="str">
-        <v/>
-      </c>
-      <c r="P15" t="str">
-        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="B16" t="str">
-        <v>q5</v>
+        <v>m5</v>
       </c>
       <c r="C16" t="str">
         <v>single</v>
@@ -1525,48 +1111,30 @@
         <v>学业自我效能</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>学生认为自己再怎么努力也学不好某些科目。</v>
       </c>
       <c r="F16" t="str">
-        <v>学生认为自己再怎么努力也学不好某些科目。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H16" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I16" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J16" t="str">
-        <v>1</v>
-      </c>
-      <c r="K16" t="str">
-        <v>是</v>
-      </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
-      <c r="M16" t="str">
         <v>compute</v>
-      </c>
-      <c r="N16" t="str">
-        <v/>
-      </c>
-      <c r="O16" t="str">
-        <v/>
-      </c>
-      <c r="P16" t="str">
-        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="B17" t="str">
-        <v>q6</v>
+        <v>m6</v>
       </c>
       <c r="C17" t="str">
         <v>single</v>
@@ -1575,52 +1143,34 @@
         <v>学业自我效能</v>
       </c>
       <c r="E17" t="str">
-        <v/>
+        <v>学生把失败归因于自己能力不行而不是方法问题。</v>
       </c>
       <c r="F17" t="str">
-        <v>学生把失败归因于自己能力不行而不是方法问题。</v>
+        <v>AGREE_5</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>否</v>
       </c>
       <c r="H17" t="str">
-        <v>AGREE_5</v>
+        <v>1</v>
       </c>
       <c r="I17" t="str">
-        <v>否</v>
+        <v>是</v>
       </c>
       <c r="J17" t="str">
-        <v>1</v>
-      </c>
-      <c r="K17" t="str">
-        <v>是</v>
-      </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
-      <c r="M17" t="str">
         <v>compute</v>
-      </c>
-      <c r="N17" t="str">
-        <v/>
-      </c>
-      <c r="O17" t="str">
-        <v/>
-      </c>
-      <c r="P17" t="str">
-        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1638,13 +1188,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>完全不符合</v>
+        <v>几乎没有</v>
       </c>
       <c r="D2" t="str">
         <v>1</v>
@@ -1652,13 +1202,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>比较不符合</v>
+        <v>很少</v>
       </c>
       <c r="D3" t="str">
         <v>2</v>
@@ -1666,13 +1216,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>一般</v>
+        <v>有时</v>
       </c>
       <c r="D4" t="str">
         <v>3</v>
@@ -1680,13 +1230,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>比较符合</v>
+        <v>经常</v>
       </c>
       <c r="D5" t="str">
         <v>4</v>
@@ -1694,28 +1244,98 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>AGREE_5</v>
+        <v>FREQ_5</v>
       </c>
       <c r="B6" t="str">
         <v>5</v>
       </c>
       <c r="C6" t="str">
-        <v>非常符合</v>
+        <v>几乎每天</v>
       </c>
       <c r="D6" t="str">
         <v>5</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B7" t="str">
+        <v>1</v>
+      </c>
+      <c r="C7" t="str">
+        <v>完全不符合</v>
+      </c>
+      <c r="D7" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2</v>
+      </c>
+      <c r="C8" t="str">
+        <v>比较不符合</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B9" t="str">
+        <v>3</v>
+      </c>
+      <c r="C9" t="str">
+        <v>一般</v>
+      </c>
+      <c r="D9" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>4</v>
+      </c>
+      <c r="C10" t="str">
+        <v>比较符合</v>
+      </c>
+      <c r="D10" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B11" t="str">
+        <v>5</v>
+      </c>
+      <c r="C11" t="str">
+        <v>非常符合</v>
+      </c>
+      <c r="D11" t="str">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:I7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1745,25 +1365,19 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
-      <c r="J1" t="str">
-        <v>常模均值</v>
-      </c>
-      <c r="K1" t="str">
-        <v>常模标准差</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B2" t="str">
-        <v>LP_S1D1</v>
+        <v>LP_BEHAVIOR</v>
       </c>
       <c r="C2" t="str">
         <v>行为层</v>
       </c>
       <c r="D2" t="str">
-        <v>q1,q2,q3,q4</v>
+        <v>beh1,beh2,beh3,beh4</v>
       </c>
       <c r="E2" t="str">
         <v>mean</v>
@@ -1780,25 +1394,19 @@
       <c r="I2" t="str">
         <v>学习行为稳定</v>
       </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B3" t="str">
-        <v>LP_S1D2</v>
+        <v>LP_COGNITION</v>
       </c>
       <c r="C3" t="str">
         <v>认知层</v>
       </c>
       <c r="D3" t="str">
-        <v>q5,q6,q7</v>
+        <v>cog1,cog2,cog3</v>
       </c>
       <c r="E3" t="str">
         <v>mean</v>
@@ -1815,25 +1423,19 @@
       <c r="I3" t="str">
         <v>认知加工顺畅</v>
       </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="B4" t="str">
-        <v>LP_S1D3</v>
+        <v>LP_RELATION</v>
       </c>
       <c r="C4" t="str">
         <v>关系层</v>
       </c>
       <c r="D4" t="str">
-        <v>q8,q9,q10</v>
+        <v>rel1,rel2,rel3</v>
       </c>
       <c r="E4" t="str">
         <v>mean</v>
@@ -1850,25 +1452,19 @@
       <c r="I4" t="str">
         <v>关系支持充分</v>
       </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="B5" t="str">
-        <v>LP_S2D1</v>
+        <v>LP_INTRINSIC</v>
       </c>
       <c r="C5" t="str">
         <v>内在动机</v>
       </c>
       <c r="D5" t="str">
-        <v>q1,q2</v>
+        <v>m1,m2</v>
       </c>
       <c r="E5" t="str">
         <v>mean</v>
@@ -1885,25 +1481,19 @@
       <c r="I5" t="str">
         <v>有内在学习兴趣</v>
       </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="B6" t="str">
-        <v>LP_S2D2</v>
+        <v>LP_ANXIETY</v>
       </c>
       <c r="C6" t="str">
         <v>学业焦虑</v>
       </c>
       <c r="D6" t="str">
-        <v>q3,q4</v>
+        <v>m3,m4</v>
       </c>
       <c r="E6" t="str">
         <v>mean</v>
@@ -1920,25 +1510,19 @@
       <c r="I6" t="str">
         <v>焦虑水平可控</v>
       </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="B7" t="str">
-        <v>LP_S2D3</v>
+        <v>LP_SELF_EFFICACY</v>
       </c>
       <c r="C7" t="str">
         <v>学业自我效能</v>
       </c>
       <c r="D7" t="str">
-        <v>q5,q6</v>
+        <v>m5,m6</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -1955,16 +1539,10 @@
       <c r="I7" t="str">
         <v>相信努力有用</v>
       </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/learning_problem/assessment.xlsx
+++ b/business-libraries/test-data/learning_problem/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:AL3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,60 +419,108 @@
         <v>适用学部*</v>
       </c>
       <c r="F1" t="str">
+        <v>适用年级</v>
+      </c>
+      <c r="G1" t="str">
+        <v>适用学科</v>
+      </c>
+      <c r="H1" t="str">
         <v>施测对象*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>施测形式*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>触发方式*</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>作答频次*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>是否必做*</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>预计用时分钟*</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
+        <v>作答时限分钟</v>
+      </c>
+      <c r="O1" t="str">
+        <v>最低题数</v>
+      </c>
+      <c r="P1" t="str">
+        <v>使用时机</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>重评间隔天数</v>
+      </c>
+      <c r="R1" t="str">
+        <v>前置量表编码</v>
+      </c>
+      <c r="S1" t="str">
+        <v>互斥量表编码</v>
+      </c>
+      <c r="T1" t="str">
+        <v>触发条件</v>
+      </c>
+      <c r="U1" t="str">
+        <v>触发条件说明</v>
+      </c>
+      <c r="V1" t="str">
+        <v>结果可见性*</v>
+      </c>
+      <c r="W1" t="str">
+        <v>责任角色</v>
+      </c>
+      <c r="X1" t="str">
+        <v>数据敏感级*</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>来源属性*</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>外部授权说明</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>手册出处*</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>版本*</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>量表说明</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>常模参照</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>信度说明</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>效度说明</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>隐私声明</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>适用前提</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>不适合情况</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>后续建议动作</v>
+      </c>
+      <c r="AK1" t="str">
         <v>量表角色*</v>
       </c>
-      <c r="M1" t="str">
-        <v>前置量表编码</v>
-      </c>
-      <c r="N1" t="str">
-        <v>互斥量表编码</v>
-      </c>
-      <c r="O1" t="str">
-        <v>触发条件</v>
-      </c>
-      <c r="P1" t="str">
-        <v>触发条件说明</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>结果可见性*</v>
-      </c>
-      <c r="R1" t="str">
-        <v>数据敏感级*</v>
-      </c>
-      <c r="S1" t="str">
-        <v>来源属性*</v>
-      </c>
-      <c r="T1" t="str">
-        <v>手册出处*</v>
-      </c>
-      <c r="U1" t="str">
-        <v>版本*</v>
-      </c>
-      <c r="V1" t="str">
-        <v>量表说明</v>
+      <c r="AL1" t="str">
+        <v>做完导向什么*</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B2" t="str">
         <v>学生学习问题三层诊断</v>
@@ -487,60 +535,108 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>teacher</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>self_report</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>manual</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>per_case</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>是</v>
       </c>
-      <c r="K2" t="str">
+      <c r="M2" t="str">
         <v>5</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W2" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X2" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>4.0.0</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>从行为、认知和关系三个层面识别学生学习困难的主导因素，不构成学习障碍诊断。</v>
+      </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
+        <v/>
+      </c>
+      <c r="AH2" t="str">
+        <v/>
+      </c>
+      <c r="AI2" t="str">
+        <v/>
+      </c>
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+      <c r="AK2" t="str">
         <v>入口筛查</v>
       </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
-      <c r="N2" t="str">
-        <v/>
-      </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2" t="str">
-        <v/>
-      </c>
-      <c r="Q2" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R2" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S2" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T2" t="str">
-        <v>学生学习问题手册v1</v>
-      </c>
-      <c r="U2" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V2" t="str">
-        <v>从行为、认知和关系三个层面识别学生学习困难的主导因素，不构成学习障碍诊断。</v>
+      <c r="AL2" t="str">
+        <v>决定要不要往下做深度诊断</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B3" t="str">
         <v>学习动机与学业情绪评估</v>
@@ -555,67 +651,115 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>teacher</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>self_report</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>manual</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>per_case</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>否</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v>6</v>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>LP_S1</v>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v>量表[LP_S1].维度[LP_S1D3] &gt;= 3 或 量表[LP_S1].均分 &gt;= 3.2</v>
+      </c>
+      <c r="U3" t="str">
+        <v>关系层卡点明显或三层整体偏重时，再深入测学习动机</v>
+      </c>
+      <c r="V3" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W3" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X3" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v>学生学习问题手册v1</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>4.0.0</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>关系层卡点明显或三层整体偏重时，再深入测学习动机</v>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
+        <v/>
+      </c>
+      <c r="AH3" t="str">
+        <v/>
+      </c>
+      <c r="AI3" t="str">
+        <v/>
+      </c>
+      <c r="AJ3" t="str">
+        <v/>
+      </c>
+      <c r="AK3" t="str">
         <v>深度诊断</v>
       </c>
-      <c r="M3" t="str">
-        <v>LP_THREE_LAYER</v>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v>量表[LP_THREE_LAYER].维度[LP_RELATION] &gt;= 3 或 量表[LP_THREE_LAYER].均分 &gt;= 3.2</v>
-      </c>
-      <c r="P3" t="str">
-        <v>关系层卡点明显或三层整体偏重时，再深入测学习动机</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>teacher_only</v>
-      </c>
-      <c r="R3" t="str">
-        <v>sensitive</v>
-      </c>
-      <c r="S3" t="str">
-        <v>proprietary</v>
-      </c>
-      <c r="T3" t="str">
-        <v>学生学习问题手册v1</v>
-      </c>
-      <c r="U3" t="str">
-        <v>1.0.0</v>
-      </c>
-      <c r="V3" t="str">
-        <v>在三层诊断提示关系层或行为层为主导后使用，用于区分动机类型和学业情绪状态。</v>
+      <c r="AL3" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:P17"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -631,30 +775,48 @@
         <v>维度*</v>
       </c>
       <c r="E1" t="str">
+        <v>子维度</v>
+      </c>
+      <c r="F1" t="str">
         <v>题干*</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>题干举例</v>
+      </c>
+      <c r="H1" t="str">
         <v>选项组编码*</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>反向计分*</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>权重</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>是否必答*</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
+        <v>显示条件</v>
+      </c>
+      <c r="M1" t="str">
         <v>数据用途*</v>
+      </c>
+      <c r="N1" t="str">
+        <v>答题提示</v>
+      </c>
+      <c r="O1" t="str">
+        <v>题目说明</v>
+      </c>
+      <c r="P1" t="str">
+        <v>默认分值</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>beh1</v>
+        <v>q1</v>
       </c>
       <c r="C2" t="str">
         <v>single</v>
@@ -663,30 +825,48 @@
         <v>行为层</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
         <v>学生经常不交或拖延完成作业。</v>
       </c>
-      <c r="F2" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I2" t="str">
         <v>否</v>
       </c>
-      <c r="H2" t="str">
-        <v>1</v>
-      </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
+        <v>1</v>
+      </c>
+      <c r="K2" t="str">
         <v>是</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>compute</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>beh2</v>
+        <v>q2</v>
       </c>
       <c r="C3" t="str">
         <v>single</v>
@@ -695,30 +875,48 @@
         <v>行为层</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
         <v>课堂上明显走神、分心或做与学习无关的事。</v>
       </c>
-      <c r="F3" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I3" t="str">
         <v>否</v>
       </c>
-      <c r="H3" t="str">
-        <v>1</v>
-      </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
+        <v>1</v>
+      </c>
+      <c r="K3" t="str">
         <v>是</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>compute</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>beh3</v>
+        <v>q3</v>
       </c>
       <c r="C4" t="str">
         <v>single</v>
@@ -727,30 +925,48 @@
         <v>行为层</v>
       </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>考试或测验成绩与实际能力之间存在明显落差。</v>
       </c>
-      <c r="F4" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I4" t="str">
         <v>否</v>
       </c>
-      <c r="H4" t="str">
-        <v>1</v>
-      </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
+        <v>1</v>
+      </c>
+      <c r="K4" t="str">
         <v>是</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>compute</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B5" t="str">
-        <v>beh4</v>
+        <v>q4</v>
       </c>
       <c r="C5" t="str">
         <v>single</v>
@@ -759,30 +975,48 @@
         <v>行为层</v>
       </c>
       <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
         <v>已有提醒或奖励措施对改善学习行为效果有限。</v>
       </c>
-      <c r="F5" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I5" t="str">
         <v>否</v>
       </c>
-      <c r="H5" t="str">
-        <v>1</v>
-      </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
+        <v>1</v>
+      </c>
+      <c r="K5" t="str">
         <v>是</v>
       </c>
-      <c r="J5" t="str">
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v>compute</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B6" t="str">
-        <v>cog1</v>
+        <v>q5</v>
       </c>
       <c r="C6" t="str">
         <v>single</v>
@@ -791,30 +1025,48 @@
         <v>认知层</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
         <v>学生对核心概念的理解停留在表面，难以迁移或应用。</v>
       </c>
-      <c r="F6" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I6" t="str">
         <v>否</v>
       </c>
-      <c r="H6" t="str">
-        <v>1</v>
-      </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
+        <v>1</v>
+      </c>
+      <c r="K6" t="str">
         <v>是</v>
       </c>
-      <c r="J6" t="str">
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v>compute</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B7" t="str">
-        <v>cog2</v>
+        <v>q6</v>
       </c>
       <c r="C7" t="str">
         <v>single</v>
@@ -823,30 +1075,48 @@
         <v>认知层</v>
       </c>
       <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
         <v>学生在记忆、推理或组织信息方面存在明显困难。</v>
       </c>
-      <c r="F7" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I7" t="str">
         <v>否</v>
       </c>
-      <c r="H7" t="str">
-        <v>1</v>
-      </c>
-      <c r="I7" t="str">
+      <c r="J7" t="str">
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
         <v>是</v>
       </c>
-      <c r="J7" t="str">
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <v>compute</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B8" t="str">
-        <v>cog3</v>
+        <v>q7</v>
       </c>
       <c r="C8" t="str">
         <v>single</v>
@@ -855,30 +1125,48 @@
         <v>认知层</v>
       </c>
       <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
         <v>学生在独立解决问题时容易卡住，缺少元认知策略。</v>
       </c>
-      <c r="F8" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I8" t="str">
         <v>否</v>
       </c>
-      <c r="H8" t="str">
-        <v>1</v>
-      </c>
-      <c r="I8" t="str">
+      <c r="J8" t="str">
+        <v>1</v>
+      </c>
+      <c r="K8" t="str">
         <v>是</v>
       </c>
-      <c r="J8" t="str">
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
         <v>compute</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B9" t="str">
-        <v>rel1</v>
+        <v>q8</v>
       </c>
       <c r="C9" t="str">
         <v>single</v>
@@ -887,30 +1175,48 @@
         <v>关系层</v>
       </c>
       <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
         <v>师生关系或课堂归属感对学生的学习动机有明显影响。</v>
       </c>
-      <c r="F9" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I9" t="str">
         <v>否</v>
       </c>
-      <c r="H9" t="str">
-        <v>1</v>
-      </c>
-      <c r="I9" t="str">
+      <c r="J9" t="str">
+        <v>1</v>
+      </c>
+      <c r="K9" t="str">
         <v>是</v>
       </c>
-      <c r="J9" t="str">
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <v>compute</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B10" t="str">
-        <v>rel2</v>
+        <v>q9</v>
       </c>
       <c r="C10" t="str">
         <v>single</v>
@@ -919,30 +1225,48 @@
         <v>关系层</v>
       </c>
       <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
         <v>同伴之间的比较、竞争或排斥影响了学生的学习投入。</v>
       </c>
-      <c r="F10" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I10" t="str">
         <v>否</v>
       </c>
-      <c r="H10" t="str">
-        <v>1</v>
-      </c>
-      <c r="I10" t="str">
+      <c r="J10" t="str">
+        <v>1</v>
+      </c>
+      <c r="K10" t="str">
         <v>是</v>
       </c>
-      <c r="J10" t="str">
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
         <v>compute</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B11" t="str">
-        <v>rel3</v>
+        <v>q10</v>
       </c>
       <c r="C11" t="str">
         <v>single</v>
@@ -951,30 +1275,48 @@
         <v>关系层</v>
       </c>
       <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
         <v>家庭对学习的支持、期待或冲突明显影响了学生的学业状态。</v>
       </c>
-      <c r="F11" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I11" t="str">
         <v>否</v>
       </c>
-      <c r="H11" t="str">
-        <v>1</v>
-      </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
+        <v>1</v>
+      </c>
+      <c r="K11" t="str">
         <v>是</v>
       </c>
-      <c r="J11" t="str">
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v>compute</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B12" t="str">
-        <v>m1</v>
+        <v>q1</v>
       </c>
       <c r="C12" t="str">
         <v>single</v>
@@ -983,30 +1325,48 @@
         <v>内在动机</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
         <v>没有老师或家长督促时，学生几乎不主动学习。</v>
       </c>
-      <c r="F12" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I12" t="str">
         <v>否</v>
       </c>
-      <c r="H12" t="str">
-        <v>1</v>
-      </c>
-      <c r="I12" t="str">
+      <c r="J12" t="str">
+        <v>1</v>
+      </c>
+      <c r="K12" t="str">
         <v>是</v>
       </c>
-      <c r="J12" t="str">
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <v>compute</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B13" t="str">
-        <v>m2</v>
+        <v>q2</v>
       </c>
       <c r="C13" t="str">
         <v>single</v>
@@ -1015,30 +1375,48 @@
         <v>内在动机</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
         <v>学生学习主要是为了避免被批评。</v>
       </c>
-      <c r="F13" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I13" t="str">
         <v>否</v>
       </c>
-      <c r="H13" t="str">
-        <v>1</v>
-      </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
+        <v>1</v>
+      </c>
+      <c r="K13" t="str">
         <v>是</v>
       </c>
-      <c r="J13" t="str">
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v>compute</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B14" t="str">
-        <v>m3</v>
+        <v>q3</v>
       </c>
       <c r="C14" t="str">
         <v>single</v>
@@ -1047,30 +1425,48 @@
         <v>学业焦虑</v>
       </c>
       <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
         <v>临近考试时学生出现明显紧张或躯体不适。</v>
       </c>
-      <c r="F14" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I14" t="str">
         <v>否</v>
       </c>
-      <c r="H14" t="str">
-        <v>1</v>
-      </c>
-      <c r="I14" t="str">
+      <c r="J14" t="str">
+        <v>1</v>
+      </c>
+      <c r="K14" t="str">
         <v>是</v>
       </c>
-      <c r="J14" t="str">
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <v>compute</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B15" t="str">
-        <v>m4</v>
+        <v>q4</v>
       </c>
       <c r="C15" t="str">
         <v>single</v>
@@ -1079,30 +1475,48 @@
         <v>学业焦虑</v>
       </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
         <v>学生因为怕出错而不敢在课堂上表达。</v>
       </c>
-      <c r="F15" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I15" t="str">
         <v>否</v>
       </c>
-      <c r="H15" t="str">
-        <v>1</v>
-      </c>
-      <c r="I15" t="str">
+      <c r="J15" t="str">
+        <v>1</v>
+      </c>
+      <c r="K15" t="str">
         <v>是</v>
       </c>
-      <c r="J15" t="str">
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
         <v>compute</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B16" t="str">
-        <v>m5</v>
+        <v>q5</v>
       </c>
       <c r="C16" t="str">
         <v>single</v>
@@ -1111,30 +1525,48 @@
         <v>学业自我效能</v>
       </c>
       <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
         <v>学生认为自己再怎么努力也学不好某些科目。</v>
       </c>
-      <c r="F16" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I16" t="str">
         <v>否</v>
       </c>
-      <c r="H16" t="str">
-        <v>1</v>
-      </c>
-      <c r="I16" t="str">
+      <c r="J16" t="str">
+        <v>1</v>
+      </c>
+      <c r="K16" t="str">
         <v>是</v>
       </c>
-      <c r="J16" t="str">
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
         <v>compute</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B17" t="str">
-        <v>m6</v>
+        <v>q6</v>
       </c>
       <c r="C17" t="str">
         <v>single</v>
@@ -1143,34 +1575,52 @@
         <v>学业自我效能</v>
       </c>
       <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
         <v>学生把失败归因于自己能力不行而不是方法问题。</v>
       </c>
-      <c r="F17" t="str">
-        <v>AGREE_5</v>
-      </c>
       <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I17" t="str">
         <v>否</v>
       </c>
-      <c r="H17" t="str">
-        <v>1</v>
-      </c>
-      <c r="I17" t="str">
+      <c r="J17" t="str">
+        <v>1</v>
+      </c>
+      <c r="K17" t="str">
         <v>是</v>
       </c>
-      <c r="J17" t="str">
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
         <v>compute</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P17"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1188,13 +1638,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>几乎没有</v>
+        <v>完全不符合</v>
       </c>
       <c r="D2" t="str">
         <v>1</v>
@@ -1202,13 +1652,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>很少</v>
+        <v>比较不符合</v>
       </c>
       <c r="D3" t="str">
         <v>2</v>
@@ -1216,13 +1666,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>有时</v>
+        <v>一般</v>
       </c>
       <c r="D4" t="str">
         <v>3</v>
@@ -1230,13 +1680,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>经常</v>
+        <v>比较符合</v>
       </c>
       <c r="D5" t="str">
         <v>4</v>
@@ -1244,98 +1694,28 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>FREQ_5</v>
+        <v>AGREE_5</v>
       </c>
       <c r="B6" t="str">
         <v>5</v>
       </c>
       <c r="C6" t="str">
-        <v>几乎每天</v>
+        <v>非常符合</v>
       </c>
       <c r="D6" t="str">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B7" t="str">
-        <v>1</v>
-      </c>
-      <c r="C7" t="str">
-        <v>完全不符合</v>
-      </c>
-      <c r="D7" t="str">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2</v>
-      </c>
-      <c r="C8" t="str">
-        <v>比较不符合</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B9" t="str">
-        <v>3</v>
-      </c>
-      <c r="C9" t="str">
-        <v>一般</v>
-      </c>
-      <c r="D9" t="str">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B10" t="str">
-        <v>4</v>
-      </c>
-      <c r="C10" t="str">
-        <v>比较符合</v>
-      </c>
-      <c r="D10" t="str">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>AGREE_5</v>
-      </c>
-      <c r="B11" t="str">
-        <v>5</v>
-      </c>
-      <c r="C11" t="str">
-        <v>非常符合</v>
-      </c>
-      <c r="D11" t="str">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:K7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1365,19 +1745,25 @@
       <c r="I1" t="str">
         <v>低分解释</v>
       </c>
+      <c r="J1" t="str">
+        <v>常模均值</v>
+      </c>
+      <c r="K1" t="str">
+        <v>常模标准差</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>LP_BEHAVIOR</v>
+        <v>LP_S1D1</v>
       </c>
       <c r="C2" t="str">
         <v>行为层</v>
       </c>
       <c r="D2" t="str">
-        <v>beh1,beh2,beh3,beh4</v>
+        <v>q1,q2,q3,q4</v>
       </c>
       <c r="E2" t="str">
         <v>mean</v>
@@ -1394,19 +1780,25 @@
       <c r="I2" t="str">
         <v>学习行为稳定</v>
       </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B3" t="str">
-        <v>LP_COGNITION</v>
+        <v>LP_S1D2</v>
       </c>
       <c r="C3" t="str">
         <v>认知层</v>
       </c>
       <c r="D3" t="str">
-        <v>cog1,cog2,cog3</v>
+        <v>q5,q6,q7</v>
       </c>
       <c r="E3" t="str">
         <v>mean</v>
@@ -1423,19 +1815,25 @@
       <c r="I3" t="str">
         <v>认知加工顺畅</v>
       </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="B4" t="str">
-        <v>LP_RELATION</v>
+        <v>LP_S1D3</v>
       </c>
       <c r="C4" t="str">
         <v>关系层</v>
       </c>
       <c r="D4" t="str">
-        <v>rel1,rel2,rel3</v>
+        <v>q8,q9,q10</v>
       </c>
       <c r="E4" t="str">
         <v>mean</v>
@@ -1452,19 +1850,25 @@
       <c r="I4" t="str">
         <v>关系支持充分</v>
       </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B5" t="str">
-        <v>LP_INTRINSIC</v>
+        <v>LP_S2D1</v>
       </c>
       <c r="C5" t="str">
         <v>内在动机</v>
       </c>
       <c r="D5" t="str">
-        <v>m1,m2</v>
+        <v>q1,q2</v>
       </c>
       <c r="E5" t="str">
         <v>mean</v>
@@ -1481,19 +1885,25 @@
       <c r="I5" t="str">
         <v>有内在学习兴趣</v>
       </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B6" t="str">
-        <v>LP_ANXIETY</v>
+        <v>LP_S2D2</v>
       </c>
       <c r="C6" t="str">
         <v>学业焦虑</v>
       </c>
       <c r="D6" t="str">
-        <v>m3,m4</v>
+        <v>q3,q4</v>
       </c>
       <c r="E6" t="str">
         <v>mean</v>
@@ -1510,19 +1920,25 @@
       <c r="I6" t="str">
         <v>焦虑水平可控</v>
       </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="B7" t="str">
-        <v>LP_SELF_EFFICACY</v>
+        <v>LP_S2D3</v>
       </c>
       <c r="C7" t="str">
         <v>学业自我效能</v>
       </c>
       <c r="D7" t="str">
-        <v>m5,m6</v>
+        <v>q5,q6</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -1539,10 +1955,16 @@
       <c r="I7" t="str">
         <v>相信努力有用</v>
       </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/learning_problem/assessment.xlsx
+++ b/business-libraries/test-data/learning_problem/assessment.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL3"/>
+  <dimension ref="A1:AL8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -523,10 +523,10 @@
         <v>LP_S1</v>
       </c>
       <c r="B2" t="str">
-        <v>学生学习问题三层诊断</v>
+        <v>SNAP-IV注意力筛查</v>
       </c>
       <c r="C2" t="str">
-        <v>三层诊断</v>
+        <v>SNAP-IV筛查</v>
       </c>
       <c r="D2" t="str">
         <v>learning_problem</v>
@@ -535,7 +535,7 @@
         <v>all</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>1,2,3,4,5,6</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -544,7 +544,7 @@
         <v>teacher</v>
       </c>
       <c r="I2" t="str">
-        <v>self_report</v>
+        <v>observation</v>
       </c>
       <c r="J2" t="str">
         <v>manual</v>
@@ -556,7 +556,7 @@
         <v>是</v>
       </c>
       <c r="M2" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N2" t="str">
         <v/>
@@ -565,10 +565,10 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v/>
+        <v>低中段（1-2·3-4年级）筛查首选，5-6年级亦可</v>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>30</v>
       </c>
       <c r="R2" t="str">
         <v/>
@@ -592,19 +592,19 @@
         <v>sensitive</v>
       </c>
       <c r="Y2" t="str">
-        <v>proprietary</v>
+        <v>adapted</v>
       </c>
       <c r="Z2" t="str">
         <v/>
       </c>
       <c r="AA2" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
       <c r="AB2" t="str">
-        <v>4.0.0</v>
+        <v>4.2.0</v>
       </c>
       <c r="AC2" t="str">
-        <v>从行为、认知和关系三个层面识别学生学习困难的主导因素，不构成学习障碍诊断。</v>
+        <v>注意力与多动筛查量表（SNAP-IV 精华版），教师与家长双评，筛查注意缺陷/多动-冲动倾向，用于学校筛查而非临床诊断。</v>
       </c>
       <c r="AD2" t="str">
         <v/>
@@ -622,10 +622,10 @@
         <v/>
       </c>
       <c r="AI2" t="str">
-        <v/>
+        <v>量表仅作筛查预警，不作临床诊断；结论不能单独作为干预或转介依据</v>
       </c>
       <c r="AJ2" t="str">
-        <v/>
+        <v>阳性结果须结合深度访谈与课堂观察交叉核实，必要时转介专业机构评估</v>
       </c>
       <c r="AK2" t="str">
         <v>入口筛查</v>
@@ -639,10 +639,10 @@
         <v>LP_S2</v>
       </c>
       <c r="B3" t="str">
-        <v>学习动机与学业情绪评估</v>
+        <v>学习策略量表</v>
       </c>
       <c r="C3" t="str">
-        <v>动机情绪</v>
+        <v>学习策略</v>
       </c>
       <c r="D3" t="str">
         <v>learning_problem</v>
@@ -651,13 +651,13 @@
         <v>all</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>3,4,5,6</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>teacher</v>
+        <v>student</v>
       </c>
       <c r="I3" t="str">
         <v>self_report</v>
@@ -672,7 +672,7 @@
         <v>否</v>
       </c>
       <c r="M3" t="str">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N3" t="str">
         <v/>
@@ -681,10 +681,10 @@
         <v/>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>3-4·5-6年级为主；低段重习惯由教师/家长代评</v>
       </c>
       <c r="Q3" t="str">
-        <v/>
+        <v>60</v>
       </c>
       <c r="R3" t="str">
         <v>LP_S1</v>
@@ -693,10 +693,10 @@
         <v/>
       </c>
       <c r="T3" t="str">
-        <v>量表[LP_S1].维度[LP_S1D3] &gt;= 3 或 量表[LP_S1].均分 &gt;= 3.2</v>
+        <v>量表[LP_S1].维度[LP_S1D1] &lt;= 1.5 且 量表[LP_S1].维度[LP_S1D2] &lt;= 1.5</v>
       </c>
       <c r="U3" t="str">
-        <v>关系层卡点明显或三层整体偏重时，再深入测学习动机</v>
+        <v>学生"努力但效率低"、不会预习复习、笔记差或元认知弱，且注意力问题不占主导时建议做</v>
       </c>
       <c r="V3" t="str">
         <v>teacher_only</v>
@@ -708,19 +708,19 @@
         <v>sensitive</v>
       </c>
       <c r="Y3" t="str">
-        <v>proprietary</v>
+        <v>adapted</v>
       </c>
       <c r="Z3" t="str">
         <v/>
       </c>
       <c r="AA3" t="str">
-        <v>学生学习问题手册v1</v>
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
       </c>
       <c r="AB3" t="str">
-        <v>4.0.0</v>
+        <v>4.2.0</v>
       </c>
       <c r="AC3" t="str">
-        <v>关系层卡点明显或三层整体偏重时，再深入测学习动机</v>
+        <v>学习策略量表（MAI/LASSI 精华版），评估认知策略与元认知策略使用水平，定位策略缺失点。</v>
       </c>
       <c r="AD3" t="str">
         <v/>
@@ -741,7 +741,7 @@
         <v/>
       </c>
       <c r="AJ3" t="str">
-        <v/>
+        <v>结合学业成绩分析区分"知识落差"与"策略落差"，转入学科策略辅导</v>
       </c>
       <c r="AK3" t="str">
         <v>深度诊断</v>
@@ -750,16 +750,596 @@
         <v>定位薄弱维度，匹配对应工具</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>学习动机量表</v>
+      </c>
+      <c r="C4" t="str">
+        <v>学习动机</v>
+      </c>
+      <c r="D4" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="E4" t="str">
+        <v>all</v>
+      </c>
+      <c r="F4" t="str">
+        <v>3,4,5,6</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v>student</v>
+      </c>
+      <c r="I4" t="str">
+        <v>self_report</v>
+      </c>
+      <c r="J4" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K4" t="str">
+        <v>per_case</v>
+      </c>
+      <c r="L4" t="str">
+        <v>否</v>
+      </c>
+      <c r="M4" t="str">
+        <v>5</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v>5-6年级为主，动机问题高段突出；3-4年级亦可评估</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>60</v>
+      </c>
+      <c r="R4" t="str">
+        <v>LP_S1</v>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v>量表[LP_S1].维度[LP_S1D1] &lt;= 1.5 且 量表[LP_S1].维度[LP_S1D2] &lt;= 1.5</v>
+      </c>
+      <c r="U4" t="str">
+        <v>学生厌学、被动学习、目标模糊或缺乏内驱力时建议做</v>
+      </c>
+      <c r="V4" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W4" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X4" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>adapted</v>
+      </c>
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+      <c r="AA4" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>4.2.0</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>学习动机量表（SDT/AMS 精华版），区分自主动机（内在/认同）与外控动机，识别无动机风险。</v>
+      </c>
+      <c r="AD4" t="str">
+        <v/>
+      </c>
+      <c r="AE4" t="str">
+        <v/>
+      </c>
+      <c r="AF4" t="str">
+        <v/>
+      </c>
+      <c r="AG4" t="str">
+        <v/>
+      </c>
+      <c r="AH4" t="str">
+        <v/>
+      </c>
+      <c r="AI4" t="str">
+        <v/>
+      </c>
+      <c r="AJ4" t="str">
+        <v>无动机或外控动机明显时先点燃动力，再谈学习方法与策略</v>
+      </c>
+      <c r="AK4" t="str">
+        <v>深度诊断</v>
+      </c>
+      <c r="AL4" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>学业情绪量表</v>
+      </c>
+      <c r="C5" t="str">
+        <v>学业情绪</v>
+      </c>
+      <c r="D5" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="E5" t="str">
+        <v>all</v>
+      </c>
+      <c r="F5" t="str">
+        <v>1,2,3,4,5,6</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v>student</v>
+      </c>
+      <c r="I5" t="str">
+        <v>self_report</v>
+      </c>
+      <c r="J5" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K5" t="str">
+        <v>per_case</v>
+      </c>
+      <c r="L5" t="str">
+        <v>否</v>
+      </c>
+      <c r="M5" t="str">
+        <v>5</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v>全学段，低段由教师/家长观察代评</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>30</v>
+      </c>
+      <c r="R5" t="str">
+        <v>LP_S1</v>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v>量表[LP_S1].维度[LP_S1D1] &gt;= 1.5 且 量表[LP_S1].维度[LP_S1D2] &gt;= 1.5</v>
+      </c>
+      <c r="U5" t="str">
+        <v>学生一提学习就烦、慌或怕，或与注意力问题同时出现时建议做</v>
+      </c>
+      <c r="V5" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W5" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X5" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>adapted</v>
+      </c>
+      <c r="Z5" t="str">
+        <v/>
+      </c>
+      <c r="AA5" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>4.2.0</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>学业情绪量表（AEQ 精华版），评估积极/消极学业情绪，识别情绪性学习困难。</v>
+      </c>
+      <c r="AD5" t="str">
+        <v/>
+      </c>
+      <c r="AE5" t="str">
+        <v/>
+      </c>
+      <c r="AF5" t="str">
+        <v/>
+      </c>
+      <c r="AG5" t="str">
+        <v/>
+      </c>
+      <c r="AH5" t="str">
+        <v/>
+      </c>
+      <c r="AI5" t="str">
+        <v/>
+      </c>
+      <c r="AJ5" t="str">
+        <v>消极情绪偏多时优先疏导情绪，情绪性困难常被误认为态度差</v>
+      </c>
+      <c r="AK5" t="str">
+        <v>深度诊断</v>
+      </c>
+      <c r="AL5" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>依恋关系评估</v>
+      </c>
+      <c r="C6" t="str">
+        <v>依恋评估</v>
+      </c>
+      <c r="D6" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="E6" t="str">
+        <v>all</v>
+      </c>
+      <c r="F6" t="str">
+        <v>1,2,3,4,5,6</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="I6" t="str">
+        <v>observation</v>
+      </c>
+      <c r="J6" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K6" t="str">
+        <v>per_case</v>
+      </c>
+      <c r="L6" t="str">
+        <v>否</v>
+      </c>
+      <c r="M6" t="str">
+        <v>5</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v>全学段，低中段重点看分离焦虑与求助回避</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>60</v>
+      </c>
+      <c r="R6" t="str">
+        <v>LP_S1</v>
+      </c>
+      <c r="S6" t="str">
+        <v/>
+      </c>
+      <c r="T6" t="str">
+        <v>量表[LP_S1].维度[LP_S1D1] &gt;= 1.5 且 量表[LP_S1].维度[LP_S1D2] &gt;= 1.5</v>
+      </c>
+      <c r="U6" t="str">
+        <v>孩子不愿求助、情绪易波动、师生或亲子冲突较多时建议做</v>
+      </c>
+      <c r="V6" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W6" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X6" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y6" t="str">
+        <v>adapted</v>
+      </c>
+      <c r="Z6" t="str">
+        <v/>
+      </c>
+      <c r="AA6" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>4.2.0</v>
+      </c>
+      <c r="AC6" t="str">
+        <v>依恋关系评估量表（IPPA 精简＋师生依恋观察），评估亲子依恋安全性，识别回避/矛盾/紊乱风险。</v>
+      </c>
+      <c r="AD6" t="str">
+        <v/>
+      </c>
+      <c r="AE6" t="str">
+        <v/>
+      </c>
+      <c r="AF6" t="str">
+        <v/>
+      </c>
+      <c r="AG6" t="str">
+        <v/>
+      </c>
+      <c r="AH6" t="str">
+        <v/>
+      </c>
+      <c r="AI6" t="str">
+        <v/>
+      </c>
+      <c r="AJ6" t="str">
+        <v>判定为不安全依恋时优先修复亲子关系，再谈学业支持</v>
+      </c>
+      <c r="AK6" t="str">
+        <v>深度诊断</v>
+      </c>
+      <c r="AL6" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>课堂观察评定</v>
+      </c>
+      <c r="C7" t="str">
+        <v>课堂观察</v>
+      </c>
+      <c r="D7" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="E7" t="str">
+        <v>all</v>
+      </c>
+      <c r="F7" t="str">
+        <v>1,2,3,4,5,6</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="I7" t="str">
+        <v>observation</v>
+      </c>
+      <c r="J7" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K7" t="str">
+        <v>per_case</v>
+      </c>
+      <c r="L7" t="str">
+        <v>否</v>
+      </c>
+      <c r="M7" t="str">
+        <v>5</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v>全学段，低段行为观察权重更高；建议每周汇总一次</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>30</v>
+      </c>
+      <c r="R7" t="str">
+        <v>LP_S1</v>
+      </c>
+      <c r="S7" t="str">
+        <v/>
+      </c>
+      <c r="T7" t="str">
+        <v>量表[LP_S1].维度[LP_S1D1] &gt;= 1.5 且 量表[LP_S1].维度[LP_S1D2] &gt;= 1.5</v>
+      </c>
+      <c r="U7" t="str">
+        <v>需要连续 1-2 周观察课堂与课间行为、交叉核实筛查结果时建议做</v>
+      </c>
+      <c r="V7" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W7" t="str">
+        <v>班主任/学科教师</v>
+      </c>
+      <c r="X7" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y7" t="str">
+        <v>adapted</v>
+      </c>
+      <c r="Z7" t="str">
+        <v/>
+      </c>
+      <c r="AA7" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>4.2.0</v>
+      </c>
+      <c r="AC7" t="str">
+        <v>课堂观察评定量表（CBRS 精简10维），班主任连续1-2周课堂观察的结构化评定。</v>
+      </c>
+      <c r="AD7" t="str">
+        <v/>
+      </c>
+      <c r="AE7" t="str">
+        <v/>
+      </c>
+      <c r="AF7" t="str">
+        <v/>
+      </c>
+      <c r="AG7" t="str">
+        <v/>
+      </c>
+      <c r="AH7" t="str">
+        <v/>
+      </c>
+      <c r="AI7" t="str">
+        <v/>
+      </c>
+      <c r="AJ7" t="str">
+        <v>任单维≤2 时重点干预，总均分&lt;3 时持续观察并给予课堂支持</v>
+      </c>
+      <c r="AK7" t="str">
+        <v>专项/情境</v>
+      </c>
+      <c r="AL7" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>LP_S7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>成绩趋势与学科诊断</v>
+      </c>
+      <c r="C8" t="str">
+        <v>成绩趋势</v>
+      </c>
+      <c r="D8" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="E8" t="str">
+        <v>all</v>
+      </c>
+      <c r="F8" t="str">
+        <v>1,2,3,4,5,6</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v>teacher</v>
+      </c>
+      <c r="I8" t="str">
+        <v>checklist</v>
+      </c>
+      <c r="J8" t="str">
+        <v>manual</v>
+      </c>
+      <c r="K8" t="str">
+        <v>per_case</v>
+      </c>
+      <c r="L8" t="str">
+        <v>否</v>
+      </c>
+      <c r="M8" t="str">
+        <v>5</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v>全学段；按学科录入近3次成绩与班级均值</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>90</v>
+      </c>
+      <c r="R8" t="str">
+        <v>LP_S1</v>
+      </c>
+      <c r="S8" t="str">
+        <v/>
+      </c>
+      <c r="T8" t="str">
+        <v>量表[LP_S1].维度[LP_S1D1] &lt;= 1.5 且 量表[LP_S1].维度[LP_S1D2] &lt;= 1.5</v>
+      </c>
+      <c r="U8" t="str">
+        <v>学生出现成绩下滑、偏科或"努力但成绩差"时建议做</v>
+      </c>
+      <c r="V8" t="str">
+        <v>teacher_only</v>
+      </c>
+      <c r="W8" t="str">
+        <v>班主任</v>
+      </c>
+      <c r="X8" t="str">
+        <v>sensitive</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>proprietary</v>
+      </c>
+      <c r="Z8" t="str">
+        <v/>
+      </c>
+      <c r="AA8" t="str">
+        <v>学习问题 2.0 三库文档（2026-07-27 版）</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>4.2.0</v>
+      </c>
+      <c r="AC8" t="str">
+        <v>学业成绩趋势与学科诊断速查：记录近3次成绩、对比班级均值，自动标记薄弱/偏科/下滑。</v>
+      </c>
+      <c r="AD8" t="str">
+        <v/>
+      </c>
+      <c r="AE8" t="str">
+        <v/>
+      </c>
+      <c r="AF8" t="str">
+        <v/>
+      </c>
+      <c r="AG8" t="str">
+        <v/>
+      </c>
+      <c r="AH8" t="str">
+        <v/>
+      </c>
+      <c r="AI8" t="str">
+        <v/>
+      </c>
+      <c r="AJ8" t="str">
+        <v>任一科第3次低于其他科均值≥15分标注偏科；≥3科连续下滑优先排查家庭/情绪因素</v>
+      </c>
+      <c r="AK8" t="str">
+        <v>专项/情境</v>
+      </c>
+      <c r="AL8" t="str">
+        <v>定位薄弱维度，匹配对应工具</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AL3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL8"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P91"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -822,19 +1402,19 @@
         <v>single</v>
       </c>
       <c r="D2" t="str">
-        <v>行为层</v>
+        <v>注意缺陷</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>学生经常不交或拖延完成作业。</v>
+        <v>很难持续专注于功课或需要动脑的任务</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="I2" t="str">
         <v>否</v>
@@ -872,19 +1452,19 @@
         <v>single</v>
       </c>
       <c r="D3" t="str">
-        <v>行为层</v>
+        <v>注意缺陷</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>课堂上明显走神、分心或做与学习无关的事。</v>
+        <v>别人对他说话时，似乎没在听</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="I3" t="str">
         <v>否</v>
@@ -922,19 +1502,19 @@
         <v>single</v>
       </c>
       <c r="D4" t="str">
-        <v>行为层</v>
+        <v>注意缺陷</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>考试或测验成绩与实际能力之间存在明显落差。</v>
+        <v>不按指示把事情做完（非对抗行为）</v>
       </c>
       <c r="G4" t="str">
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="I4" t="str">
         <v>否</v>
@@ -972,19 +1552,19 @@
         <v>single</v>
       </c>
       <c r="D5" t="str">
-        <v>行为层</v>
+        <v>注意缺陷</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>已有提醒或奖励措施对改善学习行为效果有限。</v>
+        <v>难以有条理地完成功课或活动</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="I5" t="str">
         <v>否</v>
@@ -1022,19 +1602,19 @@
         <v>single</v>
       </c>
       <c r="D6" t="str">
-        <v>认知层</v>
+        <v>注意缺陷</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>学生对核心概念的理解停留在表面，难以迁移或应用。</v>
+        <v>回避、不喜欢或勉强做需持续动脑的任务</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="I6" t="str">
         <v>否</v>
@@ -1072,19 +1652,19 @@
         <v>single</v>
       </c>
       <c r="D7" t="str">
-        <v>认知层</v>
+        <v>注意缺陷</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>学生在记忆、推理或组织信息方面存在明显困难。</v>
+        <v>遗失学习或活动所需的物品</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="I7" t="str">
         <v>否</v>
@@ -1122,19 +1702,19 @@
         <v>single</v>
       </c>
       <c r="D8" t="str">
-        <v>认知层</v>
+        <v>注意缺陷</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>学生在独立解决问题时容易卡住，缺少元认知策略。</v>
+        <v>容易被无关刺激分散注意力</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="I8" t="str">
         <v>否</v>
@@ -1172,19 +1752,19 @@
         <v>single</v>
       </c>
       <c r="D9" t="str">
-        <v>关系层</v>
+        <v>注意缺陷</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>师生关系或课堂归属感对学生的学习动机有明显影响。</v>
+        <v>日常生活中显得健忘</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="I9" t="str">
         <v>否</v>
@@ -1222,19 +1802,19 @@
         <v>single</v>
       </c>
       <c r="D10" t="str">
-        <v>关系层</v>
+        <v>注意缺陷</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>同伴之间的比较、竞争或排斥影响了学生的学习投入。</v>
+        <v>在细节上粗心，难以维持注意力</v>
       </c>
       <c r="G10" t="str">
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="I10" t="str">
         <v>否</v>
@@ -1272,19 +1852,19 @@
         <v>single</v>
       </c>
       <c r="D11" t="str">
-        <v>关系层</v>
+        <v>多动-冲动</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>家庭对学习的支持、期待或冲突明显影响了学生的学业状态。</v>
+        <v>坐着手脚动个不停或在座位上扭动</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="I11" t="str">
         <v>否</v>
@@ -1313,28 +1893,28 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>LP_S2</v>
+        <v>LP_S1</v>
       </c>
       <c r="B12" t="str">
-        <v>q1</v>
+        <v>q11</v>
       </c>
       <c r="C12" t="str">
         <v>single</v>
       </c>
       <c r="D12" t="str">
-        <v>内在动机</v>
+        <v>多动-冲动</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>没有老师或家长督促时，学生几乎不主动学习。</v>
+        <v>在需要坐好的场合（教室）离开座位</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="I12" t="str">
         <v>否</v>
@@ -1363,28 +1943,28 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>LP_S2</v>
+        <v>LP_S1</v>
       </c>
       <c r="B13" t="str">
-        <v>q2</v>
+        <v>q12</v>
       </c>
       <c r="C13" t="str">
         <v>single</v>
       </c>
       <c r="D13" t="str">
-        <v>内在动机</v>
+        <v>多动-冲动</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>学生学习主要是为了避免被批评。</v>
+        <v>在不合适的场合跑来跑去或爬上爬下</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="I13" t="str">
         <v>否</v>
@@ -1413,28 +1993,28 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>LP_S2</v>
+        <v>LP_S1</v>
       </c>
       <c r="B14" t="str">
-        <v>q3</v>
+        <v>q13</v>
       </c>
       <c r="C14" t="str">
         <v>single</v>
       </c>
       <c r="D14" t="str">
-        <v>学业焦虑</v>
+        <v>多动-冲动</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>临近考试时学生出现明显紧张或躯体不适。</v>
+        <v>难以安静地玩耍或参加休闲活动</v>
       </c>
       <c r="G14" t="str">
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="I14" t="str">
         <v>否</v>
@@ -1463,28 +2043,28 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>LP_S2</v>
+        <v>LP_S1</v>
       </c>
       <c r="B15" t="str">
-        <v>q4</v>
+        <v>q14</v>
       </c>
       <c r="C15" t="str">
         <v>single</v>
       </c>
       <c r="D15" t="str">
-        <v>学业焦虑</v>
+        <v>多动-冲动</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>学生因为怕出错而不敢在课堂上表达。</v>
+        <v>像被"马达驱动"一样停不下来</v>
       </c>
       <c r="G15" t="str">
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="I15" t="str">
         <v>否</v>
@@ -1513,28 +2093,28 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>LP_S2</v>
+        <v>LP_S1</v>
       </c>
       <c r="B16" t="str">
-        <v>q5</v>
+        <v>q15</v>
       </c>
       <c r="C16" t="str">
         <v>single</v>
       </c>
       <c r="D16" t="str">
-        <v>学业自我效能</v>
+        <v>多动-冲动</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>学生认为自己再怎么努力也学不好某些科目。</v>
+        <v>说话过多</v>
       </c>
       <c r="G16" t="str">
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="I16" t="str">
         <v>否</v>
@@ -1563,28 +2143,28 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>LP_S2</v>
+        <v>LP_S1</v>
       </c>
       <c r="B17" t="str">
-        <v>q6</v>
+        <v>q16</v>
       </c>
       <c r="C17" t="str">
         <v>single</v>
       </c>
       <c r="D17" t="str">
-        <v>学业自我效能</v>
+        <v>多动-冲动</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>学生把失败归因于自己能力不行而不是方法问题。</v>
+        <v>问题尚未问完就抢着回答</v>
       </c>
       <c r="G17" t="str">
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="I17" t="str">
         <v>否</v>
@@ -1611,16 +2191,3716 @@
         <v/>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>LP_S1</v>
+      </c>
+      <c r="B18" t="str">
+        <v>q17</v>
+      </c>
+      <c r="C18" t="str">
+        <v>single</v>
+      </c>
+      <c r="D18" t="str">
+        <v>多动-冲动</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v>难以按顺序等待（如排队）</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v>LP_OPT_01</v>
+      </c>
+      <c r="I18" t="str">
+        <v>否</v>
+      </c>
+      <c r="J18" t="str">
+        <v>1</v>
+      </c>
+      <c r="K18" t="str">
+        <v>是</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>LP_S1</v>
+      </c>
+      <c r="B19" t="str">
+        <v>q18</v>
+      </c>
+      <c r="C19" t="str">
+        <v>single</v>
+      </c>
+      <c r="D19" t="str">
+        <v>多动-冲动</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v>打断或侵扰别人（插嘴、打扰游戏）</v>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v>LP_OPT_01</v>
+      </c>
+      <c r="I19" t="str">
+        <v>否</v>
+      </c>
+      <c r="J19" t="str">
+        <v>1</v>
+      </c>
+      <c r="K19" t="str">
+        <v>是</v>
+      </c>
+      <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B20" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C20" t="str">
+        <v>single</v>
+      </c>
+      <c r="D20" t="str">
+        <v>认知-复述精细加工</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v>我会通过反复朗读或抄写帮助记忆</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I20" t="str">
+        <v>是</v>
+      </c>
+      <c r="J20" t="str">
+        <v>1</v>
+      </c>
+      <c r="K20" t="str">
+        <v>是</v>
+      </c>
+      <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B21" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C21" t="str">
+        <v>single</v>
+      </c>
+      <c r="D21" t="str">
+        <v>认知-复述精细加工</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v>我会用自己的话解释难点</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I21" t="str">
+        <v>是</v>
+      </c>
+      <c r="J21" t="str">
+        <v>1</v>
+      </c>
+      <c r="K21" t="str">
+        <v>是</v>
+      </c>
+      <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B22" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C22" t="str">
+        <v>single</v>
+      </c>
+      <c r="D22" t="str">
+        <v>认知-复述精细加工</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v>我会把新知识和旧知识联系起来</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I22" t="str">
+        <v>是</v>
+      </c>
+      <c r="J22" t="str">
+        <v>1</v>
+      </c>
+      <c r="K22" t="str">
+        <v>是</v>
+      </c>
+      <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B23" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C23" t="str">
+        <v>single</v>
+      </c>
+      <c r="D23" t="str">
+        <v>认知-复述精细加工</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v>我会举例子或打比方帮助理解</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I23" t="str">
+        <v>是</v>
+      </c>
+      <c r="J23" t="str">
+        <v>1</v>
+      </c>
+      <c r="K23" t="str">
+        <v>是</v>
+      </c>
+      <c r="L23" t="str">
+        <v/>
+      </c>
+      <c r="M23" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B24" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C24" t="str">
+        <v>single</v>
+      </c>
+      <c r="D24" t="str">
+        <v>认知-组织</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v>我会用提纲或思维导图整理内容</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I24" t="str">
+        <v>是</v>
+      </c>
+      <c r="J24" t="str">
+        <v>1</v>
+      </c>
+      <c r="K24" t="str">
+        <v>是</v>
+      </c>
+      <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B25" t="str">
+        <v>q6</v>
+      </c>
+      <c r="C25" t="str">
+        <v>single</v>
+      </c>
+      <c r="D25" t="str">
+        <v>认知-组织</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v>我会把材料分成几个部分来理解</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I25" t="str">
+        <v>是</v>
+      </c>
+      <c r="J25" t="str">
+        <v>1</v>
+      </c>
+      <c r="K25" t="str">
+        <v>是</v>
+      </c>
+      <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B26" t="str">
+        <v>q7</v>
+      </c>
+      <c r="C26" t="str">
+        <v>single</v>
+      </c>
+      <c r="D26" t="str">
+        <v>认知-组织</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v>我会抓住重点和关键词</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I26" t="str">
+        <v>是</v>
+      </c>
+      <c r="J26" t="str">
+        <v>1</v>
+      </c>
+      <c r="K26" t="str">
+        <v>是</v>
+      </c>
+      <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B27" t="str">
+        <v>q8</v>
+      </c>
+      <c r="C27" t="str">
+        <v>single</v>
+      </c>
+      <c r="D27" t="str">
+        <v>认知-组织</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v>我会比较不同内容的异同</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I27" t="str">
+        <v>是</v>
+      </c>
+      <c r="J27" t="str">
+        <v>1</v>
+      </c>
+      <c r="K27" t="str">
+        <v>是</v>
+      </c>
+      <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B28" t="str">
+        <v>q9</v>
+      </c>
+      <c r="C28" t="str">
+        <v>single</v>
+      </c>
+      <c r="D28" t="str">
+        <v>元认知-计划</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v>学习前我会先想清楚目标和步骤</v>
+      </c>
+      <c r="G28" t="str">
+        <v/>
+      </c>
+      <c r="H28" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I28" t="str">
+        <v>是</v>
+      </c>
+      <c r="J28" t="str">
+        <v>1</v>
+      </c>
+      <c r="K28" t="str">
+        <v>是</v>
+      </c>
+      <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B29" t="str">
+        <v>q10</v>
+      </c>
+      <c r="C29" t="str">
+        <v>single</v>
+      </c>
+      <c r="D29" t="str">
+        <v>元认知-计划</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v>我会为任务安排时间</v>
+      </c>
+      <c r="G29" t="str">
+        <v/>
+      </c>
+      <c r="H29" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I29" t="str">
+        <v>是</v>
+      </c>
+      <c r="J29" t="str">
+        <v>1</v>
+      </c>
+      <c r="K29" t="str">
+        <v>是</v>
+      </c>
+      <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B30" t="str">
+        <v>q11</v>
+      </c>
+      <c r="C30" t="str">
+        <v>single</v>
+      </c>
+      <c r="D30" t="str">
+        <v>元认知-计划</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v>我会把大任务拆成小步骤</v>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
+      <c r="H30" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I30" t="str">
+        <v>是</v>
+      </c>
+      <c r="J30" t="str">
+        <v>1</v>
+      </c>
+      <c r="K30" t="str">
+        <v>是</v>
+      </c>
+      <c r="L30" t="str">
+        <v/>
+      </c>
+      <c r="M30" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B31" t="str">
+        <v>q12</v>
+      </c>
+      <c r="C31" t="str">
+        <v>single</v>
+      </c>
+      <c r="D31" t="str">
+        <v>元认知-计划</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v>我会预估完成任务需要的时间</v>
+      </c>
+      <c r="G31" t="str">
+        <v/>
+      </c>
+      <c r="H31" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I31" t="str">
+        <v>是</v>
+      </c>
+      <c r="J31" t="str">
+        <v>1</v>
+      </c>
+      <c r="K31" t="str">
+        <v>是</v>
+      </c>
+      <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B32" t="str">
+        <v>q13</v>
+      </c>
+      <c r="C32" t="str">
+        <v>single</v>
+      </c>
+      <c r="D32" t="str">
+        <v>元认知-监控</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v>学习时我会检查自己是否走神</v>
+      </c>
+      <c r="G32" t="str">
+        <v/>
+      </c>
+      <c r="H32" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I32" t="str">
+        <v>是</v>
+      </c>
+      <c r="J32" t="str">
+        <v>1</v>
+      </c>
+      <c r="K32" t="str">
+        <v>是</v>
+      </c>
+      <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B33" t="str">
+        <v>q14</v>
+      </c>
+      <c r="C33" t="str">
+        <v>single</v>
+      </c>
+      <c r="D33" t="str">
+        <v>元认知-监控</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v>阅读时我会边读边问自己懂没懂</v>
+      </c>
+      <c r="G33" t="str">
+        <v/>
+      </c>
+      <c r="H33" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I33" t="str">
+        <v>是</v>
+      </c>
+      <c r="J33" t="str">
+        <v>1</v>
+      </c>
+      <c r="K33" t="str">
+        <v>是</v>
+      </c>
+      <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B34" t="str">
+        <v>q15</v>
+      </c>
+      <c r="C34" t="str">
+        <v>single</v>
+      </c>
+      <c r="D34" t="str">
+        <v>元认知-监控</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v>我会及时发现理解错误并回头重看</v>
+      </c>
+      <c r="G34" t="str">
+        <v/>
+      </c>
+      <c r="H34" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I34" t="str">
+        <v>是</v>
+      </c>
+      <c r="J34" t="str">
+        <v>1</v>
+      </c>
+      <c r="K34" t="str">
+        <v>是</v>
+      </c>
+      <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B35" t="str">
+        <v>q16</v>
+      </c>
+      <c r="C35" t="str">
+        <v>single</v>
+      </c>
+      <c r="D35" t="str">
+        <v>元认知-监控</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v>我会根据难度调整学习方法</v>
+      </c>
+      <c r="G35" t="str">
+        <v/>
+      </c>
+      <c r="H35" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I35" t="str">
+        <v>是</v>
+      </c>
+      <c r="J35" t="str">
+        <v>1</v>
+      </c>
+      <c r="K35" t="str">
+        <v>是</v>
+      </c>
+      <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B36" t="str">
+        <v>q17</v>
+      </c>
+      <c r="C36" t="str">
+        <v>single</v>
+      </c>
+      <c r="D36" t="str">
+        <v>元认知-调节资源</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v>学完我会自测是否真正掌握</v>
+      </c>
+      <c r="G36" t="str">
+        <v/>
+      </c>
+      <c r="H36" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I36" t="str">
+        <v>是</v>
+      </c>
+      <c r="J36" t="str">
+        <v>1</v>
+      </c>
+      <c r="K36" t="str">
+        <v>是</v>
+      </c>
+      <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B37" t="str">
+        <v>q18</v>
+      </c>
+      <c r="C37" t="str">
+        <v>single</v>
+      </c>
+      <c r="D37" t="str">
+        <v>元认知-调节资源</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v>遇到困难我会换一种方法再试</v>
+      </c>
+      <c r="G37" t="str">
+        <v/>
+      </c>
+      <c r="H37" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I37" t="str">
+        <v>是</v>
+      </c>
+      <c r="J37" t="str">
+        <v>1</v>
+      </c>
+      <c r="K37" t="str">
+        <v>是</v>
+      </c>
+      <c r="L37" t="str">
+        <v/>
+      </c>
+      <c r="M37" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B38" t="str">
+        <v>q19</v>
+      </c>
+      <c r="C38" t="str">
+        <v>single</v>
+      </c>
+      <c r="D38" t="str">
+        <v>元认知-调节资源</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v>我会主动向老师或同学求助</v>
+      </c>
+      <c r="G38" t="str">
+        <v/>
+      </c>
+      <c r="H38" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I38" t="str">
+        <v>是</v>
+      </c>
+      <c r="J38" t="str">
+        <v>1</v>
+      </c>
+      <c r="K38" t="str">
+        <v>是</v>
+      </c>
+      <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B39" t="str">
+        <v>q20</v>
+      </c>
+      <c r="C39" t="str">
+        <v>single</v>
+      </c>
+      <c r="D39" t="str">
+        <v>元认知-调节资源</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v>我会用错题本或复习资料巩固</v>
+      </c>
+      <c r="G39" t="str">
+        <v/>
+      </c>
+      <c r="H39" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I39" t="str">
+        <v>是</v>
+      </c>
+      <c r="J39" t="str">
+        <v>1</v>
+      </c>
+      <c r="K39" t="str">
+        <v>是</v>
+      </c>
+      <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B40" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C40" t="str">
+        <v>single</v>
+      </c>
+      <c r="D40" t="str">
+        <v>内在动机</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v>因为学习本身让我感到有趣</v>
+      </c>
+      <c r="G40" t="str">
+        <v/>
+      </c>
+      <c r="H40" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="I40" t="str">
+        <v>是</v>
+      </c>
+      <c r="J40" t="str">
+        <v>1</v>
+      </c>
+      <c r="K40" t="str">
+        <v>是</v>
+      </c>
+      <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B41" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C41" t="str">
+        <v>single</v>
+      </c>
+      <c r="D41" t="str">
+        <v>内在动机</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v>因为我喜欢探索新东西</v>
+      </c>
+      <c r="G41" t="str">
+        <v/>
+      </c>
+      <c r="H41" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="I41" t="str">
+        <v>是</v>
+      </c>
+      <c r="J41" t="str">
+        <v>1</v>
+      </c>
+      <c r="K41" t="str">
+        <v>是</v>
+      </c>
+      <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B42" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C42" t="str">
+        <v>single</v>
+      </c>
+      <c r="D42" t="str">
+        <v>内在动机</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>因为解决难题让我有成就感</v>
+      </c>
+      <c r="G42" t="str">
+        <v/>
+      </c>
+      <c r="H42" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="I42" t="str">
+        <v>是</v>
+      </c>
+      <c r="J42" t="str">
+        <v>1</v>
+      </c>
+      <c r="K42" t="str">
+        <v>是</v>
+      </c>
+      <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B43" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C43" t="str">
+        <v>single</v>
+      </c>
+      <c r="D43" t="str">
+        <v>认同调节</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v>因为学习对我实现目标很重要</v>
+      </c>
+      <c r="G43" t="str">
+        <v/>
+      </c>
+      <c r="H43" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="I43" t="str">
+        <v>是</v>
+      </c>
+      <c r="J43" t="str">
+        <v>1</v>
+      </c>
+      <c r="K43" t="str">
+        <v>是</v>
+      </c>
+      <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B44" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C44" t="str">
+        <v>single</v>
+      </c>
+      <c r="D44" t="str">
+        <v>认同调节</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v>因为我想成为有知识有能力的人</v>
+      </c>
+      <c r="G44" t="str">
+        <v/>
+      </c>
+      <c r="H44" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="I44" t="str">
+        <v>是</v>
+      </c>
+      <c r="J44" t="str">
+        <v>1</v>
+      </c>
+      <c r="K44" t="str">
+        <v>是</v>
+      </c>
+      <c r="L44" t="str">
+        <v/>
+      </c>
+      <c r="M44" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B45" t="str">
+        <v>q6</v>
+      </c>
+      <c r="C45" t="str">
+        <v>single</v>
+      </c>
+      <c r="D45" t="str">
+        <v>认同调节</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v>因为掌握本领对将来有用</v>
+      </c>
+      <c r="G45" t="str">
+        <v/>
+      </c>
+      <c r="H45" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="I45" t="str">
+        <v>是</v>
+      </c>
+      <c r="J45" t="str">
+        <v>1</v>
+      </c>
+      <c r="K45" t="str">
+        <v>是</v>
+      </c>
+      <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B46" t="str">
+        <v>q7</v>
+      </c>
+      <c r="C46" t="str">
+        <v>single</v>
+      </c>
+      <c r="D46" t="str">
+        <v>外在调节</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v>为了避免被批评或惩罚而学</v>
+      </c>
+      <c r="G46" t="str">
+        <v/>
+      </c>
+      <c r="H46" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="I46" t="str">
+        <v>否</v>
+      </c>
+      <c r="J46" t="str">
+        <v>1</v>
+      </c>
+      <c r="K46" t="str">
+        <v>是</v>
+      </c>
+      <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B47" t="str">
+        <v>q8</v>
+      </c>
+      <c r="C47" t="str">
+        <v>single</v>
+      </c>
+      <c r="D47" t="str">
+        <v>外在调节</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v>为了获得奖励或表扬而学</v>
+      </c>
+      <c r="G47" t="str">
+        <v/>
+      </c>
+      <c r="H47" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="I47" t="str">
+        <v>否</v>
+      </c>
+      <c r="J47" t="str">
+        <v>1</v>
+      </c>
+      <c r="K47" t="str">
+        <v>是</v>
+      </c>
+      <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B48" t="str">
+        <v>q9</v>
+      </c>
+      <c r="C48" t="str">
+        <v>single</v>
+      </c>
+      <c r="D48" t="str">
+        <v>外在调节</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v>因为家长/老师要求必须学</v>
+      </c>
+      <c r="G48" t="str">
+        <v/>
+      </c>
+      <c r="H48" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="I48" t="str">
+        <v>否</v>
+      </c>
+      <c r="J48" t="str">
+        <v>1</v>
+      </c>
+      <c r="K48" t="str">
+        <v>是</v>
+      </c>
+      <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B49" t="str">
+        <v>q10</v>
+      </c>
+      <c r="C49" t="str">
+        <v>single</v>
+      </c>
+      <c r="D49" t="str">
+        <v>无动机</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v>我不清楚学习到底有什么用</v>
+      </c>
+      <c r="G49" t="str">
+        <v/>
+      </c>
+      <c r="H49" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="I49" t="str">
+        <v>否</v>
+      </c>
+      <c r="J49" t="str">
+        <v>1</v>
+      </c>
+      <c r="K49" t="str">
+        <v>是</v>
+      </c>
+      <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B50" t="str">
+        <v>q11</v>
+      </c>
+      <c r="C50" t="str">
+        <v>single</v>
+      </c>
+      <c r="D50" t="str">
+        <v>无动机</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v>学不学对我都无所谓</v>
+      </c>
+      <c r="G50" t="str">
+        <v/>
+      </c>
+      <c r="H50" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="I50" t="str">
+        <v>否</v>
+      </c>
+      <c r="J50" t="str">
+        <v>1</v>
+      </c>
+      <c r="K50" t="str">
+        <v>是</v>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B51" t="str">
+        <v>q12</v>
+      </c>
+      <c r="C51" t="str">
+        <v>single</v>
+      </c>
+      <c r="D51" t="str">
+        <v>无动机</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v>我学不进去也懒得管</v>
+      </c>
+      <c r="G51" t="str">
+        <v/>
+      </c>
+      <c r="H51" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="I51" t="str">
+        <v>否</v>
+      </c>
+      <c r="J51" t="str">
+        <v>1</v>
+      </c>
+      <c r="K51" t="str">
+        <v>是</v>
+      </c>
+      <c r="L51" t="str">
+        <v/>
+      </c>
+      <c r="M51" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="B52" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C52" t="str">
+        <v>single</v>
+      </c>
+      <c r="D52" t="str">
+        <v>积极情绪</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v>听懂课时我感到开心</v>
+      </c>
+      <c r="G52" t="str">
+        <v/>
+      </c>
+      <c r="H52" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I52" t="str">
+        <v>是</v>
+      </c>
+      <c r="J52" t="str">
+        <v>1</v>
+      </c>
+      <c r="K52" t="str">
+        <v>是</v>
+      </c>
+      <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="B53" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C53" t="str">
+        <v>single</v>
+      </c>
+      <c r="D53" t="str">
+        <v>积极情绪</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v>解决难题让我愉悦</v>
+      </c>
+      <c r="G53" t="str">
+        <v/>
+      </c>
+      <c r="H53" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I53" t="str">
+        <v>是</v>
+      </c>
+      <c r="J53" t="str">
+        <v>1</v>
+      </c>
+      <c r="K53" t="str">
+        <v>是</v>
+      </c>
+      <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="B54" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C54" t="str">
+        <v>single</v>
+      </c>
+      <c r="D54" t="str">
+        <v>积极情绪</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v>我相信自己能学好</v>
+      </c>
+      <c r="G54" t="str">
+        <v/>
+      </c>
+      <c r="H54" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I54" t="str">
+        <v>是</v>
+      </c>
+      <c r="J54" t="str">
+        <v>1</v>
+      </c>
+      <c r="K54" t="str">
+        <v>是</v>
+      </c>
+      <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="B55" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C55" t="str">
+        <v>single</v>
+      </c>
+      <c r="D55" t="str">
+        <v>积极情绪</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v>我对进步充满期待</v>
+      </c>
+      <c r="G55" t="str">
+        <v/>
+      </c>
+      <c r="H55" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I55" t="str">
+        <v>是</v>
+      </c>
+      <c r="J55" t="str">
+        <v>1</v>
+      </c>
+      <c r="K55" t="str">
+        <v>是</v>
+      </c>
+      <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="B56" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C56" t="str">
+        <v>single</v>
+      </c>
+      <c r="D56" t="str">
+        <v>积极情绪</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v>取得好成绩我为自己骄傲</v>
+      </c>
+      <c r="G56" t="str">
+        <v/>
+      </c>
+      <c r="H56" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I56" t="str">
+        <v>是</v>
+      </c>
+      <c r="J56" t="str">
+        <v>1</v>
+      </c>
+      <c r="K56" t="str">
+        <v>是</v>
+      </c>
+      <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+      <c r="P56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="B57" t="str">
+        <v>q6</v>
+      </c>
+      <c r="C57" t="str">
+        <v>single</v>
+      </c>
+      <c r="D57" t="str">
+        <v>积极情绪</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v>掌握新技能我有成就感</v>
+      </c>
+      <c r="G57" t="str">
+        <v/>
+      </c>
+      <c r="H57" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I57" t="str">
+        <v>是</v>
+      </c>
+      <c r="J57" t="str">
+        <v>1</v>
+      </c>
+      <c r="K57" t="str">
+        <v>是</v>
+      </c>
+      <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+      <c r="P57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="B58" t="str">
+        <v>q7</v>
+      </c>
+      <c r="C58" t="str">
+        <v>single</v>
+      </c>
+      <c r="D58" t="str">
+        <v>消极情绪</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v>考试前我会紧张不安</v>
+      </c>
+      <c r="G58" t="str">
+        <v/>
+      </c>
+      <c r="H58" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I58" t="str">
+        <v>否</v>
+      </c>
+      <c r="J58" t="str">
+        <v>1</v>
+      </c>
+      <c r="K58" t="str">
+        <v>是</v>
+      </c>
+      <c r="L58" t="str">
+        <v/>
+      </c>
+      <c r="M58" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+      <c r="P58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="B59" t="str">
+        <v>q8</v>
+      </c>
+      <c r="C59" t="str">
+        <v>single</v>
+      </c>
+      <c r="D59" t="str">
+        <v>消极情绪</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <v>怕考不好让我担心</v>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
+      <c r="H59" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I59" t="str">
+        <v>否</v>
+      </c>
+      <c r="J59" t="str">
+        <v>1</v>
+      </c>
+      <c r="K59" t="str">
+        <v>是</v>
+      </c>
+      <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+      <c r="P59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="B60" t="str">
+        <v>q9</v>
+      </c>
+      <c r="C60" t="str">
+        <v>single</v>
+      </c>
+      <c r="D60" t="str">
+        <v>消极情绪</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v>上课时常觉得枯燥没意思</v>
+      </c>
+      <c r="G60" t="str">
+        <v/>
+      </c>
+      <c r="H60" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I60" t="str">
+        <v>否</v>
+      </c>
+      <c r="J60" t="str">
+        <v>1</v>
+      </c>
+      <c r="K60" t="str">
+        <v>是</v>
+      </c>
+      <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="B61" t="str">
+        <v>q10</v>
+      </c>
+      <c r="C61" t="str">
+        <v>single</v>
+      </c>
+      <c r="D61" t="str">
+        <v>消极情绪</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v>觉得作业单调乏味</v>
+      </c>
+      <c r="G61" t="str">
+        <v/>
+      </c>
+      <c r="H61" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I61" t="str">
+        <v>否</v>
+      </c>
+      <c r="J61" t="str">
+        <v>1</v>
+      </c>
+      <c r="K61" t="str">
+        <v>是</v>
+      </c>
+      <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="B62" t="str">
+        <v>q11</v>
+      </c>
+      <c r="C62" t="str">
+        <v>single</v>
+      </c>
+      <c r="D62" t="str">
+        <v>消极情绪</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v>成绩差时觉得自己不行</v>
+      </c>
+      <c r="G62" t="str">
+        <v/>
+      </c>
+      <c r="H62" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I62" t="str">
+        <v>否</v>
+      </c>
+      <c r="J62" t="str">
+        <v>1</v>
+      </c>
+      <c r="K62" t="str">
+        <v>是</v>
+      </c>
+      <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="B63" t="str">
+        <v>q12</v>
+      </c>
+      <c r="C63" t="str">
+        <v>single</v>
+      </c>
+      <c r="D63" t="str">
+        <v>消极情绪</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v>出错时怕被同学笑话</v>
+      </c>
+      <c r="G63" t="str">
+        <v/>
+      </c>
+      <c r="H63" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="I63" t="str">
+        <v>否</v>
+      </c>
+      <c r="J63" t="str">
+        <v>1</v>
+      </c>
+      <c r="K63" t="str">
+        <v>是</v>
+      </c>
+      <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B64" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C64" t="str">
+        <v>single</v>
+      </c>
+      <c r="D64" t="str">
+        <v>安全-亲近</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v>遇到困难时愿意主动找父母说</v>
+      </c>
+      <c r="G64" t="str">
+        <v/>
+      </c>
+      <c r="H64" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I64" t="str">
+        <v>是</v>
+      </c>
+      <c r="J64" t="str">
+        <v>1</v>
+      </c>
+      <c r="K64" t="str">
+        <v>是</v>
+      </c>
+      <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B65" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C65" t="str">
+        <v>single</v>
+      </c>
+      <c r="D65" t="str">
+        <v>安全-亲近</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v>喜欢和父母一起做事情</v>
+      </c>
+      <c r="G65" t="str">
+        <v/>
+      </c>
+      <c r="H65" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I65" t="str">
+        <v>是</v>
+      </c>
+      <c r="J65" t="str">
+        <v>1</v>
+      </c>
+      <c r="K65" t="str">
+        <v>是</v>
+      </c>
+      <c r="L65" t="str">
+        <v/>
+      </c>
+      <c r="M65" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B66" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C66" t="str">
+        <v>single</v>
+      </c>
+      <c r="D66" t="str">
+        <v>安全-亲近</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v>和父母分开一段时间后想念他们</v>
+      </c>
+      <c r="G66" t="str">
+        <v/>
+      </c>
+      <c r="H66" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I66" t="str">
+        <v>是</v>
+      </c>
+      <c r="J66" t="str">
+        <v>1</v>
+      </c>
+      <c r="K66" t="str">
+        <v>是</v>
+      </c>
+      <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B67" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C67" t="str">
+        <v>single</v>
+      </c>
+      <c r="D67" t="str">
+        <v>安全-依赖</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v>受委屈时找父母能平静下来</v>
+      </c>
+      <c r="G67" t="str">
+        <v/>
+      </c>
+      <c r="H67" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I67" t="str">
+        <v>是</v>
+      </c>
+      <c r="J67" t="str">
+        <v>1</v>
+      </c>
+      <c r="K67" t="str">
+        <v>是</v>
+      </c>
+      <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B68" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C68" t="str">
+        <v>single</v>
+      </c>
+      <c r="D68" t="str">
+        <v>安全-依赖</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v>做重要决定会参考父母意见</v>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I68" t="str">
+        <v>是</v>
+      </c>
+      <c r="J68" t="str">
+        <v>1</v>
+      </c>
+      <c r="K68" t="str">
+        <v>是</v>
+      </c>
+      <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B69" t="str">
+        <v>q6</v>
+      </c>
+      <c r="C69" t="str">
+        <v>single</v>
+      </c>
+      <c r="D69" t="str">
+        <v>安全-依赖</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v>在新环境会先看父母反应再行动</v>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+      <c r="H69" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I69" t="str">
+        <v>是</v>
+      </c>
+      <c r="J69" t="str">
+        <v>1</v>
+      </c>
+      <c r="K69" t="str">
+        <v>是</v>
+      </c>
+      <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B70" t="str">
+        <v>q7</v>
+      </c>
+      <c r="C70" t="str">
+        <v>single</v>
+      </c>
+      <c r="D70" t="str">
+        <v>安全-安全感</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v>我相信父母会支持我</v>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+      <c r="H70" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I70" t="str">
+        <v>是</v>
+      </c>
+      <c r="J70" t="str">
+        <v>1</v>
+      </c>
+      <c r="K70" t="str">
+        <v>是</v>
+      </c>
+      <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B71" t="str">
+        <v>q8</v>
+      </c>
+      <c r="C71" t="str">
+        <v>single</v>
+      </c>
+      <c r="D71" t="str">
+        <v>安全-安全感</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v>犯错后不怕被父母嫌弃</v>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+      <c r="H71" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I71" t="str">
+        <v>是</v>
+      </c>
+      <c r="J71" t="str">
+        <v>1</v>
+      </c>
+      <c r="K71" t="str">
+        <v>是</v>
+      </c>
+      <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B72" t="str">
+        <v>q9</v>
+      </c>
+      <c r="C72" t="str">
+        <v>single</v>
+      </c>
+      <c r="D72" t="str">
+        <v>安全-安全感</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <v>我觉得父母是可靠的</v>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+      <c r="H72" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I72" t="str">
+        <v>是</v>
+      </c>
+      <c r="J72" t="str">
+        <v>1</v>
+      </c>
+      <c r="K72" t="str">
+        <v>是</v>
+      </c>
+      <c r="L72" t="str">
+        <v/>
+      </c>
+      <c r="M72" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B73" t="str">
+        <v>q10</v>
+      </c>
+      <c r="C73" t="str">
+        <v>single</v>
+      </c>
+      <c r="D73" t="str">
+        <v>风险项</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v>有事宁愿憋着也不告诉父母</v>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+      <c r="H73" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I73" t="str">
+        <v>否</v>
+      </c>
+      <c r="J73" t="str">
+        <v>1</v>
+      </c>
+      <c r="K73" t="str">
+        <v>是</v>
+      </c>
+      <c r="L73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B74" t="str">
+        <v>q11</v>
+      </c>
+      <c r="C74" t="str">
+        <v>single</v>
+      </c>
+      <c r="D74" t="str">
+        <v>风险项</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <v>怕和父母亲近会受伤</v>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+      <c r="H74" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I74" t="str">
+        <v>否</v>
+      </c>
+      <c r="J74" t="str">
+        <v>1</v>
+      </c>
+      <c r="K74" t="str">
+        <v>是</v>
+      </c>
+      <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B75" t="str">
+        <v>q12</v>
+      </c>
+      <c r="C75" t="str">
+        <v>single</v>
+      </c>
+      <c r="D75" t="str">
+        <v>风险项</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <v>对父母的承诺将信将疑</v>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+      <c r="H75" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="I75" t="str">
+        <v>否</v>
+      </c>
+      <c r="J75" t="str">
+        <v>1</v>
+      </c>
+      <c r="K75" t="str">
+        <v>是</v>
+      </c>
+      <c r="L75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="P75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="B76" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C76" t="str">
+        <v>single</v>
+      </c>
+      <c r="D76" t="str">
+        <v>课堂参与</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v>课堂任务投入度</v>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+      <c r="H76" t="str">
+        <v>LP_OPT_03</v>
+      </c>
+      <c r="I76" t="str">
+        <v>是</v>
+      </c>
+      <c r="J76" t="str">
+        <v>1</v>
+      </c>
+      <c r="K76" t="str">
+        <v>是</v>
+      </c>
+      <c r="L76" t="str">
+        <v/>
+      </c>
+      <c r="M76" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="B77" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C77" t="str">
+        <v>single</v>
+      </c>
+      <c r="D77" t="str">
+        <v>课堂参与</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <v>注意力持续性</v>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+      <c r="H77" t="str">
+        <v>LP_OPT_03</v>
+      </c>
+      <c r="I77" t="str">
+        <v>是</v>
+      </c>
+      <c r="J77" t="str">
+        <v>1</v>
+      </c>
+      <c r="K77" t="str">
+        <v>是</v>
+      </c>
+      <c r="L77" t="str">
+        <v/>
+      </c>
+      <c r="M77" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="B78" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C78" t="str">
+        <v>single</v>
+      </c>
+      <c r="D78" t="str">
+        <v>课堂参与</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v>主动举手/发言</v>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+      <c r="H78" t="str">
+        <v>LP_OPT_03</v>
+      </c>
+      <c r="I78" t="str">
+        <v>是</v>
+      </c>
+      <c r="J78" t="str">
+        <v>1</v>
+      </c>
+      <c r="K78" t="str">
+        <v>是</v>
+      </c>
+      <c r="L78" t="str">
+        <v/>
+      </c>
+      <c r="M78" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="B79" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C79" t="str">
+        <v>single</v>
+      </c>
+      <c r="D79" t="str">
+        <v>学业表现</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v>听讲理解（跟得上进度）</v>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+      <c r="H79" t="str">
+        <v>LP_OPT_03</v>
+      </c>
+      <c r="I79" t="str">
+        <v>是</v>
+      </c>
+      <c r="J79" t="str">
+        <v>1</v>
+      </c>
+      <c r="K79" t="str">
+        <v>是</v>
+      </c>
+      <c r="L79" t="str">
+        <v/>
+      </c>
+      <c r="M79" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="B80" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C80" t="str">
+        <v>single</v>
+      </c>
+      <c r="D80" t="str">
+        <v>学业表现</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <v>笔记/记录习惯</v>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+      <c r="H80" t="str">
+        <v>LP_OPT_03</v>
+      </c>
+      <c r="I80" t="str">
+        <v>是</v>
+      </c>
+      <c r="J80" t="str">
+        <v>1</v>
+      </c>
+      <c r="K80" t="str">
+        <v>是</v>
+      </c>
+      <c r="L80" t="str">
+        <v/>
+      </c>
+      <c r="M80" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="B81" t="str">
+        <v>q6</v>
+      </c>
+      <c r="C81" t="str">
+        <v>single</v>
+      </c>
+      <c r="D81" t="str">
+        <v>社会情绪</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v>同伴合作表现</v>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+      <c r="H81" t="str">
+        <v>LP_OPT_03</v>
+      </c>
+      <c r="I81" t="str">
+        <v>是</v>
+      </c>
+      <c r="J81" t="str">
+        <v>1</v>
+      </c>
+      <c r="K81" t="str">
+        <v>是</v>
+      </c>
+      <c r="L81" t="str">
+        <v/>
+      </c>
+      <c r="M81" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="B82" t="str">
+        <v>q7</v>
+      </c>
+      <c r="C82" t="str">
+        <v>single</v>
+      </c>
+      <c r="D82" t="str">
+        <v>社会情绪</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v>遵守课堂规则</v>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+      <c r="H82" t="str">
+        <v>LP_OPT_03</v>
+      </c>
+      <c r="I82" t="str">
+        <v>是</v>
+      </c>
+      <c r="J82" t="str">
+        <v>1</v>
+      </c>
+      <c r="K82" t="str">
+        <v>是</v>
+      </c>
+      <c r="L82" t="str">
+        <v/>
+      </c>
+      <c r="M82" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="B83" t="str">
+        <v>q8</v>
+      </c>
+      <c r="C83" t="str">
+        <v>single</v>
+      </c>
+      <c r="D83" t="str">
+        <v>社会情绪</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v>面对困难的坚持</v>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+      <c r="H83" t="str">
+        <v>LP_OPT_03</v>
+      </c>
+      <c r="I83" t="str">
+        <v>是</v>
+      </c>
+      <c r="J83" t="str">
+        <v>1</v>
+      </c>
+      <c r="K83" t="str">
+        <v>是</v>
+      </c>
+      <c r="L83" t="str">
+        <v/>
+      </c>
+      <c r="M83" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="B84" t="str">
+        <v>q9</v>
+      </c>
+      <c r="C84" t="str">
+        <v>single</v>
+      </c>
+      <c r="D84" t="str">
+        <v>社会情绪</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v>情绪稳定性</v>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+      <c r="H84" t="str">
+        <v>LP_OPT_03</v>
+      </c>
+      <c r="I84" t="str">
+        <v>是</v>
+      </c>
+      <c r="J84" t="str">
+        <v>1</v>
+      </c>
+      <c r="K84" t="str">
+        <v>是</v>
+      </c>
+      <c r="L84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="B85" t="str">
+        <v>q10</v>
+      </c>
+      <c r="C85" t="str">
+        <v>single</v>
+      </c>
+      <c r="D85" t="str">
+        <v>学业表现</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v>作业按时提交</v>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+      <c r="H85" t="str">
+        <v>LP_OPT_03</v>
+      </c>
+      <c r="I85" t="str">
+        <v>是</v>
+      </c>
+      <c r="J85" t="str">
+        <v>1</v>
+      </c>
+      <c r="K85" t="str">
+        <v>是</v>
+      </c>
+      <c r="L85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>LP_S7</v>
+      </c>
+      <c r="B86" t="str">
+        <v>q1</v>
+      </c>
+      <c r="C86" t="str">
+        <v>single</v>
+      </c>
+      <c r="D86" t="str">
+        <v>薄弱学科</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v>语文近3次成绩低于班级均值或连续下滑</v>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+      <c r="H86" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I86" t="str">
+        <v>否</v>
+      </c>
+      <c r="J86" t="str">
+        <v>1</v>
+      </c>
+      <c r="K86" t="str">
+        <v>是</v>
+      </c>
+      <c r="L86" t="str">
+        <v/>
+      </c>
+      <c r="M86" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+      <c r="P86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>LP_S7</v>
+      </c>
+      <c r="B87" t="str">
+        <v>q2</v>
+      </c>
+      <c r="C87" t="str">
+        <v>single</v>
+      </c>
+      <c r="D87" t="str">
+        <v>薄弱学科</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v>数学近3次成绩低于班级均值或连续下滑</v>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+      <c r="H87" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I87" t="str">
+        <v>否</v>
+      </c>
+      <c r="J87" t="str">
+        <v>1</v>
+      </c>
+      <c r="K87" t="str">
+        <v>是</v>
+      </c>
+      <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="P87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>LP_S7</v>
+      </c>
+      <c r="B88" t="str">
+        <v>q3</v>
+      </c>
+      <c r="C88" t="str">
+        <v>single</v>
+      </c>
+      <c r="D88" t="str">
+        <v>薄弱学科</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v>英语近3次成绩低于班级均值或连续下滑</v>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+      <c r="H88" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I88" t="str">
+        <v>否</v>
+      </c>
+      <c r="J88" t="str">
+        <v>1</v>
+      </c>
+      <c r="K88" t="str">
+        <v>是</v>
+      </c>
+      <c r="L88" t="str">
+        <v/>
+      </c>
+      <c r="M88" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>LP_S7</v>
+      </c>
+      <c r="B89" t="str">
+        <v>q4</v>
+      </c>
+      <c r="C89" t="str">
+        <v>single</v>
+      </c>
+      <c r="D89" t="str">
+        <v>薄弱学科</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v>科学/综合近3次成绩低于班级均值或连续下滑</v>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+      <c r="H89" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I89" t="str">
+        <v>否</v>
+      </c>
+      <c r="J89" t="str">
+        <v>1</v>
+      </c>
+      <c r="K89" t="str">
+        <v>是</v>
+      </c>
+      <c r="L89" t="str">
+        <v/>
+      </c>
+      <c r="M89" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>LP_S7</v>
+      </c>
+      <c r="B90" t="str">
+        <v>q5</v>
+      </c>
+      <c r="C90" t="str">
+        <v>single</v>
+      </c>
+      <c r="D90" t="str">
+        <v>薄弱学科</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v>其他学科近3次成绩低于班级均值或连续下滑</v>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+      <c r="H90" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I90" t="str">
+        <v>否</v>
+      </c>
+      <c r="J90" t="str">
+        <v>1</v>
+      </c>
+      <c r="K90" t="str">
+        <v>是</v>
+      </c>
+      <c r="L90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>LP_S7</v>
+      </c>
+      <c r="B91" t="str">
+        <v>q6</v>
+      </c>
+      <c r="C91" t="str">
+        <v>single</v>
+      </c>
+      <c r="D91" t="str">
+        <v>整体趋势</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v>3科及以上连续下滑，存在系统性风险</v>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+      <c r="H91" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="I91" t="str">
+        <v>否</v>
+      </c>
+      <c r="J91" t="str">
+        <v>1</v>
+      </c>
+      <c r="K91" t="str">
+        <v>是</v>
+      </c>
+      <c r="L91" t="str">
+        <v/>
+      </c>
+      <c r="M91" t="str">
+        <v>compute</v>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P91"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1638,84 +5918,406 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="B2" t="str">
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <v>完全不符合</v>
+        <v>完全没有</v>
       </c>
       <c r="D2" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="B3" t="str">
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>比较不符合</v>
+        <v>偶尔（每周1-2次）</v>
       </c>
       <c r="D3" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="B4" t="str">
         <v>3</v>
       </c>
       <c r="C4" t="str">
-        <v>一般</v>
+        <v>经常（每周3-4次）</v>
       </c>
       <c r="D4" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>AGREE_5</v>
+        <v>LP_OPT_01</v>
       </c>
       <c r="B5" t="str">
         <v>4</v>
       </c>
       <c r="C5" t="str">
-        <v>比较符合</v>
+        <v>几乎每天</v>
       </c>
       <c r="D5" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>1</v>
+      </c>
+      <c r="C6" t="str">
+        <v>几乎没有</v>
+      </c>
+      <c r="D6" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2</v>
+      </c>
+      <c r="C7" t="str">
+        <v>很少</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="B8" t="str">
+        <v>3</v>
+      </c>
+      <c r="C8" t="str">
+        <v>有时</v>
+      </c>
+      <c r="D8" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="B9" t="str">
+        <v>4</v>
+      </c>
+      <c r="C9" t="str">
+        <v>经常</v>
+      </c>
+      <c r="D9" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>FREQ_5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>5</v>
+      </c>
+      <c r="C10" t="str">
+        <v>几乎每天</v>
+      </c>
+      <c r="D10" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="B11" t="str">
+        <v>1</v>
+      </c>
+      <c r="C11" t="str">
+        <v>完全不符合</v>
+      </c>
+      <c r="D11" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2</v>
+      </c>
+      <c r="C12" t="str">
+        <v>比较不符合</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="B13" t="str">
+        <v>3</v>
+      </c>
+      <c r="C13" t="str">
+        <v>有点不符合</v>
+      </c>
+      <c r="D13" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="B14" t="str">
+        <v>4</v>
+      </c>
+      <c r="C14" t="str">
+        <v>中立</v>
+      </c>
+      <c r="D14" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="B15" t="str">
+        <v>5</v>
+      </c>
+      <c r="C15" t="str">
+        <v>有点符合</v>
+      </c>
+      <c r="D15" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="B16" t="str">
+        <v>6</v>
+      </c>
+      <c r="C16" t="str">
+        <v>比较符合</v>
+      </c>
+      <c r="D16" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>LP_OPT_02</v>
+      </c>
+      <c r="B17" t="str">
+        <v>7</v>
+      </c>
+      <c r="C17" t="str">
+        <v>完全符合</v>
+      </c>
+      <c r="D17" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
         <v>AGREE_5</v>
       </c>
-      <c r="B6" t="str">
+      <c r="B18" t="str">
+        <v>1</v>
+      </c>
+      <c r="C18" t="str">
+        <v>完全不符合</v>
+      </c>
+      <c r="D18" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2</v>
+      </c>
+      <c r="C19" t="str">
+        <v>比较不符合</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B20" t="str">
+        <v>3</v>
+      </c>
+      <c r="C20" t="str">
+        <v>一般</v>
+      </c>
+      <c r="D20" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B21" t="str">
+        <v>4</v>
+      </c>
+      <c r="C21" t="str">
+        <v>比较符合</v>
+      </c>
+      <c r="D21" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>AGREE_5</v>
+      </c>
+      <c r="B22" t="str">
         <v>5</v>
       </c>
-      <c r="C6" t="str">
+      <c r="C22" t="str">
         <v>非常符合</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D22" t="str">
         <v>5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>LP_OPT_03</v>
+      </c>
+      <c r="B23" t="str">
+        <v>1</v>
+      </c>
+      <c r="C23" t="str">
+        <v>差</v>
+      </c>
+      <c r="D23" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>LP_OPT_03</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2</v>
+      </c>
+      <c r="C24" t="str">
+        <v>较弱</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>LP_OPT_03</v>
+      </c>
+      <c r="B25" t="str">
+        <v>3</v>
+      </c>
+      <c r="C25" t="str">
+        <v>一般</v>
+      </c>
+      <c r="D25" t="str">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>LP_OPT_03</v>
+      </c>
+      <c r="B26" t="str">
+        <v>4</v>
+      </c>
+      <c r="C26" t="str">
+        <v>较好</v>
+      </c>
+      <c r="D26" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>LP_OPT_03</v>
+      </c>
+      <c r="B27" t="str">
+        <v>5</v>
+      </c>
+      <c r="C27" t="str">
+        <v>优</v>
+      </c>
+      <c r="D27" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="B28" t="str">
+        <v>1</v>
+      </c>
+      <c r="C28" t="str">
+        <v>否</v>
+      </c>
+      <c r="D28" t="str">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>YES_NO</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2</v>
+      </c>
+      <c r="C29" t="str">
+        <v>是</v>
+      </c>
+      <c r="D29" t="str">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D29"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K23"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1760,10 +6362,10 @@
         <v>LP_S1D1</v>
       </c>
       <c r="C2" t="str">
-        <v>行为层</v>
+        <v>注意缺陷</v>
       </c>
       <c r="D2" t="str">
-        <v>q1,q2,q3,q4</v>
+        <v>q1,q2,q3,q4,q5,q6,q7,q8,q9</v>
       </c>
       <c r="E2" t="str">
         <v>mean</v>
@@ -1772,13 +6374,13 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>行为层维度</v>
+        <v>注意缺陷子量表（9题）</v>
       </c>
       <c r="H2" t="str">
-        <v>学习行为持续失序且外部推动无效</v>
+        <v>注意缺陷阳性项≥6项（得分≥2）提示注意缺陷倾向</v>
       </c>
       <c r="I2" t="str">
-        <v>学习行为稳定</v>
+        <v>注意无明显缺陷信号</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -1795,10 +6397,10 @@
         <v>LP_S1D2</v>
       </c>
       <c r="C3" t="str">
-        <v>认知层</v>
+        <v>多动-冲动</v>
       </c>
       <c r="D3" t="str">
-        <v>q5,q6,q7</v>
+        <v>q10,q11,q12,q13,q14,q15,q16,q17,q18</v>
       </c>
       <c r="E3" t="str">
         <v>mean</v>
@@ -1807,13 +6409,13 @@
         <v>1</v>
       </c>
       <c r="G3" t="str">
-        <v>认知层维度</v>
+        <v>多动-冲动子量表（9题）</v>
       </c>
       <c r="H3" t="str">
-        <v>理解停留表面，缺少元认知策略</v>
+        <v>多动-冲动阳性项≥6项（得分≥2）提示多动-冲动倾向</v>
       </c>
       <c r="I3" t="str">
-        <v>认知加工顺畅</v>
+        <v>无多动-冲动信号</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -1824,16 +6426,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>LP_S1</v>
+        <v>LP_S2</v>
       </c>
       <c r="B4" t="str">
-        <v>LP_S1D3</v>
+        <v>LP_S2D1</v>
       </c>
       <c r="C4" t="str">
-        <v>关系层</v>
+        <v>认知-复述精细加工</v>
       </c>
       <c r="D4" t="str">
-        <v>q8,q9,q10</v>
+        <v>q1,q2,q3,q4</v>
       </c>
       <c r="E4" t="str">
         <v>mean</v>
@@ -1842,13 +6444,13 @@
         <v>1</v>
       </c>
       <c r="G4" t="str">
-        <v>关系层维度</v>
+        <v>复述与精细加工策略（4题）</v>
       </c>
       <c r="H4" t="str">
-        <v>师生、同伴或家庭关系明显影响学习投入</v>
+        <v>复述/精细加工策略缺失，靠死记硬背</v>
       </c>
       <c r="I4" t="str">
-        <v>关系支持充分</v>
+        <v>有复述与精细加工策略</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -1862,13 +6464,13 @@
         <v>LP_S2</v>
       </c>
       <c r="B5" t="str">
-        <v>LP_S2D1</v>
+        <v>LP_S2D2</v>
       </c>
       <c r="C5" t="str">
-        <v>内在动机</v>
+        <v>认知-组织</v>
       </c>
       <c r="D5" t="str">
-        <v>q1,q2</v>
+        <v>q5,q6,q7,q8</v>
       </c>
       <c r="E5" t="str">
         <v>mean</v>
@@ -1877,13 +6479,13 @@
         <v>1</v>
       </c>
       <c r="G5" t="str">
-        <v>内在动机维度</v>
+        <v>组织策略（4题）</v>
       </c>
       <c r="H5" t="str">
-        <v>学习完全依赖外部推动</v>
+        <v>不会提纲/思维导图等组织策略</v>
       </c>
       <c r="I5" t="str">
-        <v>有内在学习兴趣</v>
+        <v>能有效组织信息</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -1897,13 +6499,13 @@
         <v>LP_S2</v>
       </c>
       <c r="B6" t="str">
-        <v>LP_S2D2</v>
+        <v>LP_S2D3</v>
       </c>
       <c r="C6" t="str">
-        <v>学业焦虑</v>
+        <v>元认知-计划</v>
       </c>
       <c r="D6" t="str">
-        <v>q3,q4</v>
+        <v>q9,q10,q11,q12</v>
       </c>
       <c r="E6" t="str">
         <v>mean</v>
@@ -1912,13 +6514,13 @@
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v>学业焦虑维度</v>
+        <v>计划策略（4题）</v>
       </c>
       <c r="H6" t="str">
-        <v>学业焦虑明显影响表现</v>
+        <v>学习前无目标无计划</v>
       </c>
       <c r="I6" t="str">
-        <v>焦虑水平可控</v>
+        <v>学习前有计划</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -1932,13 +6534,13 @@
         <v>LP_S2</v>
       </c>
       <c r="B7" t="str">
-        <v>LP_S2D3</v>
+        <v>LP_S2D4</v>
       </c>
       <c r="C7" t="str">
-        <v>学业自我效能</v>
+        <v>元认知-监控</v>
       </c>
       <c r="D7" t="str">
-        <v>q5,q6</v>
+        <v>q13,q14,q15,q16</v>
       </c>
       <c r="E7" t="str">
         <v>mean</v>
@@ -1947,24 +6549,584 @@
         <v>1</v>
       </c>
       <c r="G7" t="str">
-        <v>学业自我效能维度</v>
+        <v>监控策略（4题）</v>
       </c>
       <c r="H7" t="str">
-        <v>认为自己学不会，习得性无助</v>
+        <v>边学边查意识弱，学完不知会不会</v>
       </c>
       <c r="I7" t="str">
-        <v>相信努力有用</v>
+        <v>能自我监控理解</v>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
       <c r="K7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="B8" t="str">
+        <v>LP_S2D5</v>
+      </c>
+      <c r="C8" t="str">
+        <v>元认知-调节资源</v>
+      </c>
+      <c r="D8" t="str">
+        <v>q17,q18,q19,q20</v>
+      </c>
+      <c r="E8" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F8" t="str">
+        <v>1</v>
+      </c>
+      <c r="G8" t="str">
+        <v>调节与资源策略（4题）</v>
+      </c>
+      <c r="H8" t="str">
+        <v>不会换方法、不求助、不用错题本</v>
+      </c>
+      <c r="I8" t="str">
+        <v>能调节方法善用资源</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B9" t="str">
+        <v>LP_S3D1</v>
+      </c>
+      <c r="C9" t="str">
+        <v>内在动机</v>
+      </c>
+      <c r="D9" t="str">
+        <v>q1,q2,q3</v>
+      </c>
+      <c r="E9" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F9" t="str">
+        <v>1</v>
+      </c>
+      <c r="G9" t="str">
+        <v>内在动机（3题）</v>
+      </c>
+      <c r="H9" t="str">
+        <v>内在动机不足，学习完全依赖外部推动</v>
+      </c>
+      <c r="I9" t="str">
+        <v>有内在学习兴趣</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B10" t="str">
+        <v>LP_S3D2</v>
+      </c>
+      <c r="C10" t="str">
+        <v>认同调节</v>
+      </c>
+      <c r="D10" t="str">
+        <v>q4,q5,q6</v>
+      </c>
+      <c r="E10" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F10" t="str">
+        <v>1</v>
+      </c>
+      <c r="G10" t="str">
+        <v>认同调节（3题）</v>
+      </c>
+      <c r="H10" t="str">
+        <v>对学习价值认同不足</v>
+      </c>
+      <c r="I10" t="str">
+        <v>认同学习价值</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B11" t="str">
+        <v>LP_S3D3</v>
+      </c>
+      <c r="C11" t="str">
+        <v>外在调节</v>
+      </c>
+      <c r="D11" t="str">
+        <v>q7,q8,q9</v>
+      </c>
+      <c r="E11" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F11" t="str">
+        <v>1</v>
+      </c>
+      <c r="G11" t="str">
+        <v>外在调节（3题）</v>
+      </c>
+      <c r="H11" t="str">
+        <v>为奖励/惩罚而学，外控主导</v>
+      </c>
+      <c r="I11" t="str">
+        <v>外控压力小</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="B12" t="str">
+        <v>LP_S3D4</v>
+      </c>
+      <c r="C12" t="str">
+        <v>无动机</v>
+      </c>
+      <c r="D12" t="str">
+        <v>q10,q11,q12</v>
+      </c>
+      <c r="E12" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F12" t="str">
+        <v>1</v>
+      </c>
+      <c r="G12" t="str">
+        <v>无动机（3题）</v>
+      </c>
+      <c r="H12" t="str">
+        <v>无动机明显，学习失去意义感</v>
+      </c>
+      <c r="I12" t="str">
+        <v>无明显无动机信号</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="B13" t="str">
+        <v>LP_S4D1</v>
+      </c>
+      <c r="C13" t="str">
+        <v>积极情绪</v>
+      </c>
+      <c r="D13" t="str">
+        <v>q1,q2,q3,q4,q5,q6</v>
+      </c>
+      <c r="E13" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F13" t="str">
+        <v>1</v>
+      </c>
+      <c r="G13" t="str">
+        <v>积极情绪（享受/希望/自豪，6题）</v>
+      </c>
+      <c r="H13" t="str">
+        <v>积极学业情绪不足</v>
+      </c>
+      <c r="I13" t="str">
+        <v>积极情绪充足</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="B14" t="str">
+        <v>LP_S4D2</v>
+      </c>
+      <c r="C14" t="str">
+        <v>消极情绪</v>
+      </c>
+      <c r="D14" t="str">
+        <v>q7,q8,q9,q10,q11,q12</v>
+      </c>
+      <c r="E14" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F14" t="str">
+        <v>1</v>
+      </c>
+      <c r="G14" t="str">
+        <v>消极情绪（焦虑/无聊/羞耻，6题）</v>
+      </c>
+      <c r="H14" t="str">
+        <v>消极情绪频繁，堵住学习</v>
+      </c>
+      <c r="I14" t="str">
+        <v>消极情绪少</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B15" t="str">
+        <v>LP_S5D1</v>
+      </c>
+      <c r="C15" t="str">
+        <v>安全-亲近</v>
+      </c>
+      <c r="D15" t="str">
+        <v>q1,q2,q3</v>
+      </c>
+      <c r="E15" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F15" t="str">
+        <v>1</v>
+      </c>
+      <c r="G15" t="str">
+        <v>亲近维度（3题）</v>
+      </c>
+      <c r="H15" t="str">
+        <v>与父母亲近不足</v>
+      </c>
+      <c r="I15" t="str">
+        <v>与父母亲近良好</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B16" t="str">
+        <v>LP_S5D2</v>
+      </c>
+      <c r="C16" t="str">
+        <v>安全-依赖</v>
+      </c>
+      <c r="D16" t="str">
+        <v>q4,q5,q6</v>
+      </c>
+      <c r="E16" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F16" t="str">
+        <v>1</v>
+      </c>
+      <c r="G16" t="str">
+        <v>依赖维度（3题）</v>
+      </c>
+      <c r="H16" t="str">
+        <v>遇到困难不愿向父母求助</v>
+      </c>
+      <c r="I16" t="str">
+        <v>能安心依赖父母</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B17" t="str">
+        <v>LP_S5D3</v>
+      </c>
+      <c r="C17" t="str">
+        <v>安全-安全感</v>
+      </c>
+      <c r="D17" t="str">
+        <v>q7,q8,q9</v>
+      </c>
+      <c r="E17" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F17" t="str">
+        <v>1</v>
+      </c>
+      <c r="G17" t="str">
+        <v>安全感维度（3题）</v>
+      </c>
+      <c r="H17" t="str">
+        <v>对父母支持缺乏安全感</v>
+      </c>
+      <c r="I17" t="str">
+        <v>对父母有安全感</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="B18" t="str">
+        <v>LP_S5D4</v>
+      </c>
+      <c r="C18" t="str">
+        <v>风险项</v>
+      </c>
+      <c r="D18" t="str">
+        <v>q10,q11,q12</v>
+      </c>
+      <c r="E18" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F18" t="str">
+        <v>1</v>
+      </c>
+      <c r="G18" t="str">
+        <v>风险项（回避/矛盾/紊乱，3题）</v>
+      </c>
+      <c r="H18" t="str">
+        <v>回避/矛盾/紊乱倾向明显</v>
+      </c>
+      <c r="I18" t="str">
+        <v>无显著风险信号</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="B19" t="str">
+        <v>LP_S6D1</v>
+      </c>
+      <c r="C19" t="str">
+        <v>课堂参与</v>
+      </c>
+      <c r="D19" t="str">
+        <v>q1,q2,q3</v>
+      </c>
+      <c r="E19" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F19" t="str">
+        <v>1</v>
+      </c>
+      <c r="G19" t="str">
+        <v>课堂参与维度（3题）</v>
+      </c>
+      <c r="H19" t="str">
+        <v>课堂投入、举手发言少</v>
+      </c>
+      <c r="I19" t="str">
+        <v>课堂参与积极</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="B20" t="str">
+        <v>LP_S6D2</v>
+      </c>
+      <c r="C20" t="str">
+        <v>学业表现</v>
+      </c>
+      <c r="D20" t="str">
+        <v>q4,q5,q10</v>
+      </c>
+      <c r="E20" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F20" t="str">
+        <v>1</v>
+      </c>
+      <c r="G20" t="str">
+        <v>学业表现维度（3题）</v>
+      </c>
+      <c r="H20" t="str">
+        <v>听讲理解、笔记、作业提交弱</v>
+      </c>
+      <c r="I20" t="str">
+        <v>学业表现良好</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="B21" t="str">
+        <v>LP_S6D3</v>
+      </c>
+      <c r="C21" t="str">
+        <v>社会情绪</v>
+      </c>
+      <c r="D21" t="str">
+        <v>q6,q7,q8,q9</v>
+      </c>
+      <c r="E21" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F21" t="str">
+        <v>1</v>
+      </c>
+      <c r="G21" t="str">
+        <v>社会情绪维度（4题）</v>
+      </c>
+      <c r="H21" t="str">
+        <v>合作、守规、坚持、情绪稳定差</v>
+      </c>
+      <c r="I21" t="str">
+        <v>社会情绪良好</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>LP_S7</v>
+      </c>
+      <c r="B22" t="str">
+        <v>LP_S7D1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>薄弱学科</v>
+      </c>
+      <c r="D22" t="str">
+        <v>q1,q2,q3,q4,q5</v>
+      </c>
+      <c r="E22" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F22" t="str">
+        <v>1</v>
+      </c>
+      <c r="G22" t="str">
+        <v>单科薄弱/偏科信号（5题）</v>
+      </c>
+      <c r="H22" t="str">
+        <v>存在薄弱或偏科学科</v>
+      </c>
+      <c r="I22" t="str">
+        <v>无偏科信号</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>LP_S7</v>
+      </c>
+      <c r="B23" t="str">
+        <v>LP_S7D2</v>
+      </c>
+      <c r="C23" t="str">
+        <v>整体趋势</v>
+      </c>
+      <c r="D23" t="str">
+        <v>q6</v>
+      </c>
+      <c r="E23" t="str">
+        <v>mean</v>
+      </c>
+      <c r="F23" t="str">
+        <v>1</v>
+      </c>
+      <c r="G23" t="str">
+        <v>多科下滑系统性风险（1题）</v>
+      </c>
+      <c r="H23" t="str">
+        <v>多科同时下滑，系统性风险</v>
+      </c>
+      <c r="I23" t="str">
+        <v>无系统性下滑</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K23"/>
   </ignoredErrors>
 </worksheet>
 </file>